--- a/dados/relatorio.xlsx
+++ b/dados/relatorio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amaggicombr-my.sharepoint.com/personal/hiago_andre_amaggi_com_br/Documents/Área de Trabalho/codigos/catalogoPecasPCM/dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="28" documentId="11_FD86FE4AC4094E4AB971B8A5A011EE841C83CB4A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1898B56E-0270-4CCE-89CF-176199A75649}"/>
+  <xr:revisionPtr revIDLastSave="30" documentId="11_FD86FE4AC4094E4AB971B8A5A011EE841C83CB4A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F31DA33E-3725-45B6-9A41-AC71D0FF43E8}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4956" uniqueCount="1587">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4956" uniqueCount="1585">
   <si>
     <t/>
   </si>
@@ -2761,9 +2761,6 @@
     <t>PARAF CAB FRANC PORC 5/16X3P UNC AC 8.8</t>
   </si>
   <si>
-    <t>4.448</t>
-  </si>
-  <si>
     <t>412413</t>
   </si>
   <si>
@@ -2845,9 +2842,6 @@
     <t>PARAFUSO PHILLIPS 4X30MM AC</t>
   </si>
   <si>
-    <t>59</t>
-  </si>
-  <si>
     <t>1010085360</t>
   </si>
   <si>
@@ -4225,9 +4219,6 @@
     <t>CORRENTE ELO 1/4P 6.4MM AG KG</t>
   </si>
   <si>
-    <t>109</t>
-  </si>
-  <si>
     <t>68</t>
   </si>
   <si>
@@ -4285,9 +4276,6 @@
     <t>CAMISA MAS COLAR LONGA AZ MAR P C/LOGO</t>
   </si>
   <si>
-    <t>248</t>
-  </si>
-  <si>
     <t>1040077388</t>
   </si>
   <si>
@@ -4300,9 +4288,6 @@
     <t>64</t>
   </si>
   <si>
-    <t>369</t>
-  </si>
-  <si>
     <t>1010083462</t>
   </si>
   <si>
@@ -4447,24 +4432,15 @@
     <t>1.192</t>
   </si>
   <si>
-    <t>220</t>
-  </si>
-  <si>
     <t>447</t>
   </si>
   <si>
-    <t>153</t>
-  </si>
-  <si>
     <t>1030000366</t>
   </si>
   <si>
     <t>PNEU 295/80 R22.5 BANDA RT51 REC</t>
   </si>
   <si>
-    <t>333</t>
-  </si>
-  <si>
     <t>67</t>
   </si>
   <si>
@@ -4474,15 +4450,6 @@
     <t>TAMBOR CARRETA RANDON/100000142456</t>
   </si>
   <si>
-    <t>135.003,500</t>
-  </si>
-  <si>
-    <t>581</t>
-  </si>
-  <si>
-    <t>199</t>
-  </si>
-  <si>
     <t>306790</t>
   </si>
   <si>
@@ -4501,9 +4468,6 @@
     <t>280</t>
   </si>
   <si>
-    <t>148</t>
-  </si>
-  <si>
     <t>175</t>
   </si>
   <si>
@@ -4519,9 +4483,6 @@
     <t>196</t>
   </si>
   <si>
-    <t>448</t>
-  </si>
-  <si>
     <t>475,220</t>
   </si>
   <si>
@@ -4534,12 +4495,6 @@
     <t>61</t>
   </si>
   <si>
-    <t>120</t>
-  </si>
-  <si>
-    <t>236</t>
-  </si>
-  <si>
     <t>79</t>
   </si>
   <si>
@@ -4549,57 +4504,24 @@
     <t>428</t>
   </si>
   <si>
-    <t>152</t>
-  </si>
-  <si>
     <t>73,500</t>
   </si>
   <si>
-    <t>620</t>
-  </si>
-  <si>
     <t>350</t>
   </si>
   <si>
     <t>532</t>
   </si>
   <si>
-    <t>941</t>
-  </si>
-  <si>
     <t>45</t>
   </si>
   <si>
-    <t>721</t>
-  </si>
-  <si>
-    <t>511</t>
-  </si>
-  <si>
     <t>1.599,390</t>
   </si>
   <si>
-    <t>702</t>
-  </si>
-  <si>
-    <t>84</t>
-  </si>
-  <si>
-    <t>3.517</t>
-  </si>
-  <si>
     <t>355</t>
   </si>
   <si>
-    <t>440</t>
-  </si>
-  <si>
-    <t>684</t>
-  </si>
-  <si>
-    <t>1.022</t>
-  </si>
-  <si>
     <t>621</t>
   </si>
   <si>
@@ -4609,126 +4531,30 @@
     <t>ARRUELA PL LI 32MM 48MM 2,65MM A C</t>
   </si>
   <si>
-    <t>385</t>
-  </si>
-  <si>
-    <t>1.069</t>
-  </si>
-  <si>
-    <t>479</t>
-  </si>
-  <si>
-    <t>1.759</t>
-  </si>
-  <si>
-    <t>74</t>
-  </si>
-  <si>
-    <t>134</t>
-  </si>
-  <si>
     <t>610</t>
   </si>
   <si>
-    <t>203</t>
-  </si>
-  <si>
-    <t>596</t>
-  </si>
-  <si>
-    <t>216</t>
-  </si>
-  <si>
-    <t>226</t>
-  </si>
-  <si>
-    <t>76</t>
-  </si>
-  <si>
-    <t>399</t>
-  </si>
-  <si>
-    <t>245</t>
-  </si>
-  <si>
-    <t>833</t>
-  </si>
-  <si>
-    <t>950</t>
-  </si>
-  <si>
     <t>257</t>
   </si>
   <si>
     <t>132</t>
   </si>
   <si>
-    <t>194</t>
-  </si>
-  <si>
-    <t>348</t>
-  </si>
-  <si>
     <t>215</t>
   </si>
   <si>
-    <t>47,200</t>
-  </si>
-  <si>
-    <t>1.156</t>
-  </si>
-  <si>
-    <t>310</t>
-  </si>
-  <si>
-    <t>137</t>
-  </si>
-  <si>
-    <t>1.470</t>
-  </si>
-  <si>
-    <t>527</t>
-  </si>
-  <si>
-    <t>2.016</t>
-  </si>
-  <si>
     <t>1.949</t>
   </si>
   <si>
-    <t>340</t>
-  </si>
-  <si>
     <t>2.842</t>
   </si>
   <si>
-    <t>46</t>
-  </si>
-  <si>
     <t>1030000370</t>
   </si>
   <si>
     <t>PNEU 295/80 R22.5 BANDA RT78 REC</t>
   </si>
   <si>
-    <t>711</t>
-  </si>
-  <si>
-    <t>498</t>
-  </si>
-  <si>
-    <t>869</t>
-  </si>
-  <si>
-    <t>217</t>
-  </si>
-  <si>
-    <t>184</t>
-  </si>
-  <si>
-    <t>34.660</t>
-  </si>
-  <si>
     <t>278</t>
   </si>
   <si>
@@ -4744,12 +4570,6 @@
     <t>57</t>
   </si>
   <si>
-    <t>787</t>
-  </si>
-  <si>
-    <t>660</t>
-  </si>
-  <si>
     <t>377363</t>
   </si>
   <si>
@@ -4765,38 +4585,206 @@
     <t>58</t>
   </si>
   <si>
-    <t>3.554,610</t>
-  </si>
-  <si>
-    <t>10.321,150</t>
-  </si>
-  <si>
-    <t>1.317</t>
-  </si>
-  <si>
-    <t>8.777</t>
-  </si>
-  <si>
-    <t>133.000,500</t>
-  </si>
-  <si>
     <t>0,008</t>
+  </si>
+  <si>
+    <t>3.437</t>
+  </si>
+  <si>
+    <t>663</t>
+  </si>
+  <si>
+    <t>1.014</t>
+  </si>
+  <si>
+    <t>1.039</t>
+  </si>
+  <si>
+    <t>135</t>
+  </si>
+  <si>
+    <t>459</t>
+  </si>
+  <si>
+    <t>569</t>
+  </si>
+  <si>
+    <t>363</t>
+  </si>
+  <si>
+    <t>1.724</t>
+  </si>
+  <si>
+    <t>351</t>
+  </si>
+  <si>
+    <t>69</t>
+  </si>
+  <si>
+    <t>189</t>
+  </si>
+  <si>
+    <t>170</t>
+  </si>
+  <si>
+    <t>130</t>
+  </si>
+  <si>
+    <t>201</t>
+  </si>
+  <si>
+    <t>566</t>
+  </si>
+  <si>
+    <t>416</t>
+  </si>
+  <si>
+    <t>208</t>
+  </si>
+  <si>
+    <t>218</t>
+  </si>
+  <si>
+    <t>326</t>
+  </si>
+  <si>
+    <t>78</t>
+  </si>
+  <si>
+    <t>387</t>
+  </si>
+  <si>
+    <t>243</t>
+  </si>
+  <si>
+    <t>817</t>
+  </si>
+  <si>
+    <t>863</t>
+  </si>
+  <si>
+    <t>224</t>
+  </si>
+  <si>
+    <t>1040077377</t>
+  </si>
+  <si>
+    <t>KIT EMBUCHA RANDON: 303000010</t>
+  </si>
+  <si>
+    <t>253</t>
+  </si>
+  <si>
+    <t>146</t>
+  </si>
+  <si>
+    <t>214</t>
+  </si>
+  <si>
+    <t>86</t>
+  </si>
+  <si>
+    <t>346</t>
+  </si>
+  <si>
+    <t>204</t>
+  </si>
+  <si>
+    <t>1.108</t>
+  </si>
+  <si>
+    <t>286</t>
+  </si>
+  <si>
+    <t>373</t>
+  </si>
+  <si>
+    <t>1.430</t>
+  </si>
+  <si>
+    <t>517</t>
+  </si>
+  <si>
+    <t>4.440</t>
+  </si>
+  <si>
+    <t>2.012</t>
+  </si>
+  <si>
+    <t>600</t>
+  </si>
+  <si>
+    <t>717</t>
+  </si>
+  <si>
+    <t>305</t>
+  </si>
+  <si>
+    <t>935</t>
+  </si>
+  <si>
+    <t>169</t>
+  </si>
+  <si>
+    <t>697</t>
+  </si>
+  <si>
+    <t>457</t>
+  </si>
+  <si>
+    <t>861</t>
+  </si>
+  <si>
+    <t>505</t>
+  </si>
+  <si>
+    <t>303</t>
+  </si>
+  <si>
+    <t>155</t>
+  </si>
+  <si>
+    <t>34.270</t>
+  </si>
+  <si>
+    <t>349</t>
+  </si>
+  <si>
+    <t>82</t>
+  </si>
+  <si>
+    <t>690</t>
+  </si>
+  <si>
+    <t>773</t>
+  </si>
+  <si>
+    <t>648</t>
+  </si>
+  <si>
+    <t>3.514,610</t>
+  </si>
+  <si>
+    <t>10.307,950</t>
+  </si>
+  <si>
+    <t>1.299</t>
+  </si>
+  <si>
+    <t>8.750</t>
+  </si>
+  <si>
+    <t>131.713,500</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -4824,14 +4812,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -5188,20 +5173,20 @@
       <c r="A1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>1378</v>
+      <c r="B1" s="1" t="s">
+        <v>1376</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>1381</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>1380</v>
-      </c>
-      <c r="F1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>1379</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>1378</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>1377</v>
       </c>
       <c r="G1" t="s">
         <v>3</v>
@@ -5244,7 +5229,7 @@
         <v>7</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>9</v>
@@ -5290,7 +5275,7 @@
         <v>7</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>30</v>
+        <v>160</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>9</v>
@@ -5528,7 +5513,7 @@
       <c r="G15" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="I15" s="2"/>
+      <c r="I15" s="1"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
@@ -5613,7 +5598,7 @@
         <v>7</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>1522</v>
+        <v>1499</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>9</v>
@@ -5705,7 +5690,7 @@
         <v>7</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>1523</v>
+        <v>1493</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>9</v>
@@ -5774,7 +5759,7 @@
         <v>7</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>9</v>
@@ -5811,10 +5796,10 @@
         <v>4</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>7</v>
@@ -5866,7 +5851,7 @@
         <v>7</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>37</v>
+        <v>921</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>9</v>
@@ -5889,7 +5874,7 @@
         <v>7</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>1147</v>
+        <v>1145</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>9</v>
@@ -5935,7 +5920,7 @@
         <v>7</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>1425</v>
+        <v>1393</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>9</v>
@@ -5958,7 +5943,7 @@
         <v>7</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>1481</v>
+        <v>1393</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>9</v>
@@ -5981,7 +5966,7 @@
         <v>7</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>23</v>
+        <v>87</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>9</v>
@@ -6004,7 +5989,7 @@
         <v>7</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>9</v>
@@ -6027,7 +6012,7 @@
         <v>7</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>9</v>
@@ -6050,7 +6035,7 @@
         <v>7</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>1481</v>
+        <v>1473</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>9</v>
@@ -6096,7 +6081,7 @@
         <v>7</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>1526</v>
+        <v>1500</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>9</v>
@@ -6156,16 +6141,16 @@
         <v>4</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>1527</v>
+        <v>1501</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>1528</v>
+        <v>1502</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>1529</v>
+        <v>274</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>9</v>
@@ -6188,7 +6173,7 @@
         <v>7</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>1530</v>
+        <v>1525</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>9</v>
@@ -6211,7 +6196,7 @@
         <v>7</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>1469</v>
+        <v>1526</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>9</v>
@@ -6234,7 +6219,7 @@
         <v>7</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>1531</v>
+        <v>1527</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>9</v>
@@ -6257,7 +6242,7 @@
         <v>7</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>1485</v>
+        <v>1528</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>9</v>
@@ -6280,7 +6265,7 @@
         <v>7</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>1426</v>
+        <v>1529</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>9</v>
@@ -6326,7 +6311,7 @@
         <v>7</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>1532</v>
+        <v>1530</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>9</v>
@@ -6556,7 +6541,7 @@
         <v>7</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>9</v>
@@ -6639,16 +6624,16 @@
         <v>4</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>1427</v>
+        <v>1422</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>1428</v>
+        <v>1423</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>160</v>
+        <v>8</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>9</v>
@@ -6671,7 +6656,7 @@
         <v>7</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>55</v>
+        <v>82</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>9</v>
@@ -7099,10 +7084,10 @@
         <v>4</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="D84" s="1" t="s">
         <v>42</v>
@@ -7269,7 +7254,7 @@
         <v>42</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>115</v>
+        <v>157</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>186</v>
@@ -7338,7 +7323,7 @@
         <v>42</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>37</v>
+        <v>410</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>186</v>
@@ -7651,10 +7636,10 @@
         <v>4</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="D108" s="1" t="s">
         <v>42</v>
@@ -7683,7 +7668,7 @@
         <v>42</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>30</v>
+        <v>163</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>186</v>
@@ -8028,7 +8013,7 @@
         <v>7</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>270</v>
+        <v>451</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>9</v>
@@ -8074,7 +8059,7 @@
         <v>7</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>274</v>
+        <v>1531</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>9</v>
@@ -8120,7 +8105,7 @@
         <v>7</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>9</v>
@@ -8143,7 +8128,7 @@
         <v>7</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>1534</v>
+        <v>1505</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>9</v>
@@ -8166,7 +8151,7 @@
         <v>7</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>1535</v>
+        <v>1503</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>9</v>
@@ -8327,7 +8312,7 @@
         <v>7</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>1486</v>
+        <v>1533</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>295</v>
@@ -8350,7 +8335,7 @@
         <v>19</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>1470</v>
+        <v>1465</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>295</v>
@@ -8419,7 +8404,7 @@
         <v>7</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>34</v>
+        <v>349</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>9</v>
@@ -8442,7 +8427,7 @@
         <v>19</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>9</v>
@@ -8465,7 +8450,7 @@
         <v>7</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>237</v>
+        <v>115</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>9</v>
@@ -8548,10 +8533,10 @@
         <v>4</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>1487</v>
+        <v>1476</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>1488</v>
+        <v>1477</v>
       </c>
       <c r="D147" s="1" t="s">
         <v>0</v>
@@ -8571,10 +8556,10 @@
         <v>4</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>1489</v>
+        <v>1478</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>1490</v>
+        <v>1479</v>
       </c>
       <c r="D148" s="1" t="s">
         <v>0</v>
@@ -8755,10 +8740,10 @@
         <v>4</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>1429</v>
+        <v>1424</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>1430</v>
+        <v>1425</v>
       </c>
       <c r="D156" s="1" t="s">
         <v>309</v>
@@ -8847,16 +8832,16 @@
         <v>4</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>1431</v>
+        <v>1426</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>1432</v>
+        <v>1427</v>
       </c>
       <c r="D160" s="1" t="s">
         <v>309</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>18</v>
+        <v>163</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>9</v>
@@ -8893,10 +8878,10 @@
         <v>4</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>1433</v>
+        <v>1428</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>1434</v>
+        <v>1429</v>
       </c>
       <c r="D162" s="1" t="s">
         <v>309</v>
@@ -8916,10 +8901,10 @@
         <v>4</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>1435</v>
+        <v>1430</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>1436</v>
+        <v>1431</v>
       </c>
       <c r="D163" s="1" t="s">
         <v>309</v>
@@ -8939,10 +8924,10 @@
         <v>4</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>1437</v>
+        <v>1432</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>1438</v>
+        <v>1433</v>
       </c>
       <c r="D164" s="1" t="s">
         <v>309</v>
@@ -8985,16 +8970,16 @@
         <v>4</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>1439</v>
+        <v>1434</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>1440</v>
+        <v>1435</v>
       </c>
       <c r="D166" s="1" t="s">
         <v>309</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>18</v>
+        <v>170</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>9</v>
@@ -9017,7 +9002,7 @@
         <v>309</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>1491</v>
+        <v>1534</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>9</v>
@@ -9100,10 +9085,10 @@
         <v>4</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>1441</v>
+        <v>1436</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>1442</v>
+        <v>1437</v>
       </c>
       <c r="D171" s="1" t="s">
         <v>309</v>
@@ -9123,10 +9108,10 @@
         <v>4</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>1443</v>
+        <v>1438</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>1444</v>
+        <v>1439</v>
       </c>
       <c r="D172" s="1" t="s">
         <v>309</v>
@@ -9146,10 +9131,10 @@
         <v>4</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>1413</v>
+        <v>1410</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>1414</v>
+        <v>1411</v>
       </c>
       <c r="D173" s="1" t="s">
         <v>309</v>
@@ -9169,10 +9154,10 @@
         <v>4</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>1415</v>
+        <v>1412</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>1416</v>
+        <v>1413</v>
       </c>
       <c r="D174" s="1" t="s">
         <v>309</v>
@@ -9192,10 +9177,10 @@
         <v>4</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>1417</v>
+        <v>1414</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>1418</v>
+        <v>1415</v>
       </c>
       <c r="D175" s="1" t="s">
         <v>309</v>
@@ -9215,10 +9200,10 @@
         <v>4</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>1419</v>
+        <v>1416</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>1420</v>
+        <v>1417</v>
       </c>
       <c r="D176" s="1" t="s">
         <v>309</v>
@@ -9293,7 +9278,7 @@
         <v>309</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>9</v>
@@ -9316,7 +9301,7 @@
         <v>309</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>1492</v>
+        <v>1481</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>9</v>
@@ -9339,7 +9324,7 @@
         <v>309</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>1493</v>
+        <v>1464</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>9</v>
@@ -9362,7 +9347,7 @@
         <v>309</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>1494</v>
+        <v>1482</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>9</v>
@@ -9385,7 +9370,7 @@
         <v>309</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>1495</v>
+        <v>1483</v>
       </c>
       <c r="F183" s="1" t="s">
         <v>9</v>
@@ -9408,7 +9393,7 @@
         <v>309</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>1496</v>
+        <v>1484</v>
       </c>
       <c r="F184" s="1" t="s">
         <v>9</v>
@@ -9431,7 +9416,7 @@
         <v>309</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>1403</v>
+        <v>1400</v>
       </c>
       <c r="F185" s="1" t="s">
         <v>9</v>
@@ -9477,7 +9462,7 @@
         <v>309</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>1497</v>
+        <v>1535</v>
       </c>
       <c r="F187" s="1" t="s">
         <v>9</v>
@@ -9523,7 +9508,7 @@
         <v>309</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>1498</v>
+        <v>1486</v>
       </c>
       <c r="F189" s="1" t="s">
         <v>9</v>
@@ -9546,7 +9531,7 @@
         <v>309</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>1402</v>
+        <v>1399</v>
       </c>
       <c r="F190" s="1" t="s">
         <v>9</v>
@@ -9753,7 +9738,7 @@
         <v>7</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>20</v>
+        <v>1445</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>9</v>
@@ -9776,7 +9761,7 @@
         <v>7</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>1472</v>
+        <v>27</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>9</v>
@@ -9937,7 +9922,7 @@
         <v>7</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>27</v>
+        <v>1497</v>
       </c>
       <c r="F207" s="1" t="s">
         <v>9</v>
@@ -9983,7 +9968,7 @@
         <v>7</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>160</v>
+        <v>46</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>9</v>
@@ -10098,7 +10083,7 @@
         <v>7</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>1499</v>
+        <v>1538</v>
       </c>
       <c r="F214" s="1" t="s">
         <v>9</v>
@@ -10328,7 +10313,7 @@
         <v>7</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>1147</v>
+        <v>1145</v>
       </c>
       <c r="F224" s="1" t="s">
         <v>9</v>
@@ -10466,7 +10451,7 @@
         <v>42</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>1344</v>
+        <v>1342</v>
       </c>
       <c r="F230" s="1" t="s">
         <v>9</v>
@@ -10512,7 +10497,7 @@
         <v>462</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>1500</v>
+        <v>1487</v>
       </c>
       <c r="F232" s="1" t="s">
         <v>463</v>
@@ -10581,7 +10566,7 @@
         <v>7</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>1460</v>
+        <v>1455</v>
       </c>
       <c r="F235" s="1" t="s">
         <v>112</v>
@@ -10627,7 +10612,7 @@
         <v>7</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="F237" s="1" t="s">
         <v>9</v>
@@ -10696,7 +10681,7 @@
         <v>7</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="F240" s="1" t="s">
         <v>9</v>
@@ -10857,7 +10842,7 @@
         <v>7</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>1445</v>
+        <v>1440</v>
       </c>
       <c r="F247" s="1" t="s">
         <v>295</v>
@@ -10880,7 +10865,7 @@
         <v>7</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="F248" s="1" t="s">
         <v>9</v>
@@ -10917,10 +10902,10 @@
         <v>4</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="C250" s="1" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="D250" s="1" t="s">
         <v>7</v>
@@ -10949,7 +10934,7 @@
         <v>7</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>1473</v>
+        <v>1468</v>
       </c>
       <c r="F251" s="1" t="s">
         <v>9</v>
@@ -10972,7 +10957,7 @@
         <v>19</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>1446</v>
+        <v>1441</v>
       </c>
       <c r="F252" s="1" t="s">
         <v>9</v>
@@ -10995,7 +10980,7 @@
         <v>7</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>1480</v>
+        <v>1541</v>
       </c>
       <c r="F253" s="1" t="s">
         <v>9</v>
@@ -11018,7 +11003,7 @@
         <v>7</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>30</v>
+        <v>163</v>
       </c>
       <c r="F254" s="1" t="s">
         <v>9</v>
@@ -11064,7 +11049,7 @@
         <v>7</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>563</v>
+        <v>1542</v>
       </c>
       <c r="F256" s="1" t="s">
         <v>9</v>
@@ -11110,7 +11095,7 @@
         <v>7</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>1466</v>
+        <v>1461</v>
       </c>
       <c r="F258" s="1" t="s">
         <v>9</v>
@@ -11271,7 +11256,7 @@
         <v>33</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>1540</v>
+        <v>1393</v>
       </c>
       <c r="F265" s="1" t="s">
         <v>9</v>
@@ -11317,7 +11302,7 @@
         <v>7</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>1501</v>
+        <v>1488</v>
       </c>
       <c r="F267" s="1" t="s">
         <v>9</v>
@@ -11340,7 +11325,7 @@
         <v>19</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>1502</v>
+        <v>1489</v>
       </c>
       <c r="F268" s="1" t="s">
         <v>9</v>
@@ -11501,7 +11486,7 @@
         <v>7</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>1503</v>
+        <v>1490</v>
       </c>
       <c r="F275" s="1" t="s">
         <v>9</v>
@@ -11570,7 +11555,7 @@
         <v>7</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>1504</v>
+        <v>1489</v>
       </c>
       <c r="F278" s="1" t="s">
         <v>9</v>
@@ -11708,7 +11693,7 @@
         <v>7</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>157</v>
+        <v>55</v>
       </c>
       <c r="F284" s="1" t="s">
         <v>9</v>
@@ -11938,7 +11923,7 @@
         <v>7</v>
       </c>
       <c r="E294" s="1" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="F294" s="1" t="s">
         <v>112</v>
@@ -11984,7 +11969,7 @@
         <v>7</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>1542</v>
+        <v>1420</v>
       </c>
       <c r="F296" s="1" t="s">
         <v>9</v>
@@ -12076,7 +12061,7 @@
         <v>7</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>1539</v>
+        <v>1448</v>
       </c>
       <c r="F300" s="1" t="s">
         <v>9</v>
@@ -12145,7 +12130,7 @@
         <v>7</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>1457</v>
+        <v>1452</v>
       </c>
       <c r="F303" s="1" t="s">
         <v>9</v>
@@ -12168,7 +12153,7 @@
         <v>7</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>1412</v>
+        <v>1409</v>
       </c>
       <c r="F304" s="1" t="s">
         <v>9</v>
@@ -12191,7 +12176,7 @@
         <v>7</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>1481</v>
+        <v>658</v>
       </c>
       <c r="F305" s="1" t="s">
         <v>9</v>
@@ -12237,7 +12222,7 @@
         <v>7</v>
       </c>
       <c r="E307" s="1" t="s">
-        <v>211</v>
+        <v>921</v>
       </c>
       <c r="F307" s="1" t="s">
         <v>9</v>
@@ -12283,7 +12268,7 @@
         <v>7</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="F309" s="1" t="s">
         <v>9</v>
@@ -12306,7 +12291,7 @@
         <v>7</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>141</v>
+        <v>237</v>
       </c>
       <c r="F310" s="1" t="s">
         <v>9</v>
@@ -12398,7 +12383,7 @@
         <v>7</v>
       </c>
       <c r="E314" s="1" t="s">
-        <v>1421</v>
+        <v>1544</v>
       </c>
       <c r="F314" s="1" t="s">
         <v>9</v>
@@ -12513,7 +12498,7 @@
         <v>7</v>
       </c>
       <c r="E319" s="1" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
       <c r="F319" s="1" t="s">
         <v>9</v>
@@ -12573,10 +12558,10 @@
         <v>4</v>
       </c>
       <c r="B322" s="1" t="s">
-        <v>1447</v>
+        <v>1442</v>
       </c>
       <c r="C322" s="1" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="D322" s="1" t="s">
         <v>7</v>
@@ -12628,7 +12613,7 @@
         <v>7</v>
       </c>
       <c r="E324" s="1" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="F324" s="1" t="s">
         <v>9</v>
@@ -12743,7 +12728,7 @@
         <v>7</v>
       </c>
       <c r="E329" s="1" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
       <c r="F329" s="1" t="s">
         <v>9</v>
@@ -12766,7 +12751,7 @@
         <v>19</v>
       </c>
       <c r="E330" s="1" t="s">
-        <v>1461</v>
+        <v>1456</v>
       </c>
       <c r="F330" s="1" t="s">
         <v>9</v>
@@ -12858,7 +12843,7 @@
         <v>7</v>
       </c>
       <c r="E334" s="1" t="s">
-        <v>1462</v>
+        <v>1457</v>
       </c>
       <c r="F334" s="1" t="s">
         <v>9</v>
@@ -12881,7 +12866,7 @@
         <v>7</v>
       </c>
       <c r="E335" s="1" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="F335" s="1" t="s">
         <v>9</v>
@@ -12904,7 +12889,7 @@
         <v>33</v>
       </c>
       <c r="E336" s="1" t="s">
-        <v>1481</v>
+        <v>658</v>
       </c>
       <c r="F336" s="1" t="s">
         <v>9</v>
@@ -13088,7 +13073,7 @@
         <v>7</v>
       </c>
       <c r="E344" s="1" t="s">
-        <v>1545</v>
+        <v>1504</v>
       </c>
       <c r="F344" s="1" t="s">
         <v>9</v>
@@ -13111,7 +13096,7 @@
         <v>7</v>
       </c>
       <c r="E345" s="1" t="s">
-        <v>1474</v>
+        <v>1469</v>
       </c>
       <c r="F345" s="1" t="s">
         <v>9</v>
@@ -13134,7 +13119,7 @@
         <v>7</v>
       </c>
       <c r="E346" s="1" t="s">
-        <v>1505</v>
+        <v>1547</v>
       </c>
       <c r="F346" s="1" t="s">
         <v>9</v>
@@ -13148,16 +13133,16 @@
         <v>4</v>
       </c>
       <c r="B347" s="1" t="s">
-        <v>696</v>
+        <v>1548</v>
       </c>
       <c r="C347" s="1" t="s">
-        <v>697</v>
+        <v>1549</v>
       </c>
       <c r="D347" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E347" s="1" t="s">
-        <v>170</v>
+        <v>812</v>
       </c>
       <c r="F347" s="1" t="s">
         <v>9</v>
@@ -13171,16 +13156,16 @@
         <v>4</v>
       </c>
       <c r="B348" s="1" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="C348" s="1" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="D348" s="1" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E348" s="1" t="s">
-        <v>700</v>
+        <v>170</v>
       </c>
       <c r="F348" s="1" t="s">
         <v>9</v>
@@ -13194,16 +13179,16 @@
         <v>4</v>
       </c>
       <c r="B349" s="1" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="C349" s="1" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="D349" s="1" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E349" s="1" t="s">
-        <v>1506</v>
+        <v>700</v>
       </c>
       <c r="F349" s="1" t="s">
         <v>9</v>
@@ -13217,16 +13202,16 @@
         <v>4</v>
       </c>
       <c r="B350" s="1" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="C350" s="1" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="D350" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E350" s="1" t="s">
-        <v>1545</v>
+        <v>1389</v>
       </c>
       <c r="F350" s="1" t="s">
         <v>9</v>
@@ -13240,16 +13225,16 @@
         <v>4</v>
       </c>
       <c r="B351" s="1" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="C351" s="1" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="D351" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E351" s="1" t="s">
-        <v>1507</v>
+        <v>1550</v>
       </c>
       <c r="F351" s="1" t="s">
         <v>9</v>
@@ -13263,16 +13248,16 @@
         <v>4</v>
       </c>
       <c r="B352" s="1" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="C352" s="1" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="D352" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E352" s="1" t="s">
-        <v>1546</v>
+        <v>1492</v>
       </c>
       <c r="F352" s="1" t="s">
         <v>9</v>
@@ -13286,19 +13271,19 @@
         <v>4</v>
       </c>
       <c r="B353" s="1" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="C353" s="1" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="D353" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E353" s="1" t="s">
-        <v>1508</v>
+        <v>1505</v>
       </c>
       <c r="F353" s="1" t="s">
-        <v>112</v>
+        <v>9</v>
       </c>
       <c r="G353" s="1" t="s">
         <v>10</v>
@@ -13315,10 +13300,10 @@
         <v>710</v>
       </c>
       <c r="D354" s="1" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E354" s="1" t="s">
-        <v>711</v>
+        <v>1538</v>
       </c>
       <c r="F354" s="1" t="s">
         <v>112</v>
@@ -13332,19 +13317,19 @@
         <v>4</v>
       </c>
       <c r="B355" s="1" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="C355" s="1" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="D355" s="1" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E355" s="1" t="s">
-        <v>1509</v>
+        <v>711</v>
       </c>
       <c r="F355" s="1" t="s">
-        <v>9</v>
+        <v>112</v>
       </c>
       <c r="G355" s="1" t="s">
         <v>10</v>
@@ -13355,16 +13340,16 @@
         <v>4</v>
       </c>
       <c r="B356" s="1" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="C356" s="1" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="D356" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E356" s="1" t="s">
-        <v>1475</v>
+        <v>1551</v>
       </c>
       <c r="F356" s="1" t="s">
         <v>9</v>
@@ -13378,16 +13363,16 @@
         <v>4</v>
       </c>
       <c r="B357" s="1" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="C357" s="1" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="D357" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E357" s="1" t="s">
-        <v>97</v>
+        <v>1552</v>
       </c>
       <c r="F357" s="1" t="s">
         <v>9</v>
@@ -13401,16 +13386,16 @@
         <v>4</v>
       </c>
       <c r="B358" s="1" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C358" s="1" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="D358" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E358" s="1" t="s">
-        <v>1547</v>
+        <v>97</v>
       </c>
       <c r="F358" s="1" t="s">
         <v>9</v>
@@ -13424,16 +13409,16 @@
         <v>4</v>
       </c>
       <c r="B359" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="C359" s="1" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="D359" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E359" s="1" t="s">
-        <v>466</v>
+        <v>1514</v>
       </c>
       <c r="F359" s="1" t="s">
         <v>9</v>
@@ -13447,16 +13432,16 @@
         <v>4</v>
       </c>
       <c r="B360" s="1" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="C360" s="1" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="D360" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E360" s="1" t="s">
-        <v>1548</v>
+        <v>1553</v>
       </c>
       <c r="F360" s="1" t="s">
         <v>9</v>
@@ -13470,16 +13455,16 @@
         <v>4</v>
       </c>
       <c r="B361" s="1" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="C361" s="1" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="D361" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E361" s="1" t="s">
-        <v>116</v>
+        <v>1554</v>
       </c>
       <c r="F361" s="1" t="s">
         <v>9</v>
@@ -13493,16 +13478,16 @@
         <v>4</v>
       </c>
       <c r="B362" s="1" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="C362" s="1" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="D362" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E362" s="1" t="s">
-        <v>644</v>
+        <v>116</v>
       </c>
       <c r="F362" s="1" t="s">
         <v>9</v>
@@ -13516,16 +13501,16 @@
         <v>4</v>
       </c>
       <c r="B363" s="1" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="C363" s="1" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="D363" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E363" s="1" t="s">
-        <v>116</v>
+        <v>23</v>
       </c>
       <c r="F363" s="1" t="s">
         <v>9</v>
@@ -13539,16 +13524,16 @@
         <v>4</v>
       </c>
       <c r="B364" s="1" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="C364" s="1" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="D364" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E364" s="1" t="s">
-        <v>18</v>
+        <v>563</v>
       </c>
       <c r="F364" s="1" t="s">
         <v>9</v>
@@ -13562,16 +13547,16 @@
         <v>4</v>
       </c>
       <c r="B365" s="1" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="C365" s="1" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="D365" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E365" s="1" t="s">
-        <v>163</v>
+        <v>18</v>
       </c>
       <c r="F365" s="1" t="s">
         <v>9</v>
@@ -13585,16 +13570,16 @@
         <v>4</v>
       </c>
       <c r="B366" s="1" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="C366" s="1" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="D366" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E366" s="1" t="s">
-        <v>30</v>
+        <v>163</v>
       </c>
       <c r="F366" s="1" t="s">
         <v>9</v>
@@ -13608,16 +13593,16 @@
         <v>4</v>
       </c>
       <c r="B367" s="1" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="C367" s="1" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="D367" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E367" s="1" t="s">
-        <v>242</v>
+        <v>30</v>
       </c>
       <c r="F367" s="1" t="s">
         <v>9</v>
@@ -13631,16 +13616,16 @@
         <v>4</v>
       </c>
       <c r="B368" s="1" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="C368" s="1" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="D368" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E368" s="1" t="s">
-        <v>121</v>
+        <v>242</v>
       </c>
       <c r="F368" s="1" t="s">
         <v>9</v>
@@ -13654,16 +13639,16 @@
         <v>4</v>
       </c>
       <c r="B369" s="1" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="C369" s="1" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="D369" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E369" s="1" t="s">
-        <v>279</v>
+        <v>121</v>
       </c>
       <c r="F369" s="1" t="s">
         <v>9</v>
@@ -13677,16 +13662,16 @@
         <v>4</v>
       </c>
       <c r="B370" s="1" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="C370" s="1" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="D370" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E370" s="1" t="s">
-        <v>30</v>
+        <v>279</v>
       </c>
       <c r="F370" s="1" t="s">
         <v>9</v>
@@ -13700,16 +13685,16 @@
         <v>4</v>
       </c>
       <c r="B371" s="1" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="C371" s="1" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="D371" s="1" t="s">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="E371" s="1" t="s">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="F371" s="1" t="s">
         <v>9</v>
@@ -13723,16 +13708,16 @@
         <v>4</v>
       </c>
       <c r="B372" s="1" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="C372" s="1" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="D372" s="1" t="s">
         <v>42</v>
       </c>
       <c r="E372" s="1" t="s">
-        <v>410</v>
+        <v>72</v>
       </c>
       <c r="F372" s="1" t="s">
         <v>9</v>
@@ -13746,16 +13731,16 @@
         <v>4</v>
       </c>
       <c r="B373" s="1" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="C373" s="1" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="D373" s="1" t="s">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="E373" s="1" t="s">
-        <v>170</v>
+        <v>410</v>
       </c>
       <c r="F373" s="1" t="s">
         <v>9</v>
@@ -13769,16 +13754,16 @@
         <v>4</v>
       </c>
       <c r="B374" s="1" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="C374" s="1" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="D374" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E374" s="1" t="s">
-        <v>55</v>
+        <v>170</v>
       </c>
       <c r="F374" s="1" t="s">
         <v>9</v>
@@ -13792,16 +13777,16 @@
         <v>4</v>
       </c>
       <c r="B375" s="1" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="C375" s="1" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="D375" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E375" s="1" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
       <c r="F375" s="1" t="s">
         <v>9</v>
@@ -13815,16 +13800,16 @@
         <v>4</v>
       </c>
       <c r="B376" s="1" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="C376" s="1" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="D376" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E376" s="1" t="s">
-        <v>170</v>
+        <v>97</v>
       </c>
       <c r="F376" s="1" t="s">
         <v>9</v>
@@ -13838,19 +13823,19 @@
         <v>4</v>
       </c>
       <c r="B377" s="1" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="C377" s="1" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="D377" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E377" s="1" t="s">
-        <v>1503</v>
+        <v>170</v>
       </c>
       <c r="F377" s="1" t="s">
-        <v>112</v>
+        <v>9</v>
       </c>
       <c r="G377" s="1" t="s">
         <v>10</v>
@@ -13861,19 +13846,19 @@
         <v>4</v>
       </c>
       <c r="B378" s="1" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="C378" s="1" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="D378" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E378" s="1" t="s">
-        <v>658</v>
+        <v>1520</v>
       </c>
       <c r="F378" s="1" t="s">
-        <v>9</v>
+        <v>112</v>
       </c>
       <c r="G378" s="1" t="s">
         <v>10</v>
@@ -13884,16 +13869,16 @@
         <v>4</v>
       </c>
       <c r="B379" s="1" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="C379" s="1" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D379" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E379" s="1" t="s">
-        <v>1510</v>
+        <v>658</v>
       </c>
       <c r="F379" s="1" t="s">
         <v>9</v>
@@ -13907,16 +13892,16 @@
         <v>4</v>
       </c>
       <c r="B380" s="1" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="C380" s="1" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="D380" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E380" s="1" t="s">
-        <v>67</v>
+        <v>1494</v>
       </c>
       <c r="F380" s="1" t="s">
         <v>9</v>
@@ -13930,16 +13915,16 @@
         <v>4</v>
       </c>
       <c r="B381" s="1" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="C381" s="1" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="D381" s="1" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E381" s="1" t="s">
-        <v>271</v>
+        <v>67</v>
       </c>
       <c r="F381" s="1" t="s">
         <v>9</v>
@@ -13953,16 +13938,16 @@
         <v>4</v>
       </c>
       <c r="B382" s="1" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="C382" s="1" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="D382" s="1" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E382" s="1" t="s">
-        <v>8</v>
+        <v>271</v>
       </c>
       <c r="F382" s="1" t="s">
         <v>9</v>
@@ -13982,10 +13967,10 @@
         <v>767</v>
       </c>
       <c r="D383" s="1" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E383" s="1" t="s">
-        <v>271</v>
+        <v>8</v>
       </c>
       <c r="F383" s="1" t="s">
         <v>9</v>
@@ -13999,19 +13984,19 @@
         <v>4</v>
       </c>
       <c r="B384" s="1" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="C384" s="1" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="D384" s="1" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="E384" s="1" t="s">
-        <v>8</v>
+        <v>271</v>
       </c>
       <c r="F384" s="1" t="s">
-        <v>463</v>
+        <v>9</v>
       </c>
       <c r="G384" s="1" t="s">
         <v>10</v>
@@ -14022,19 +14007,19 @@
         <v>4</v>
       </c>
       <c r="B385" s="1" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="C385" s="1" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="D385" s="1" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="E385" s="1" t="s">
-        <v>466</v>
+        <v>8</v>
       </c>
       <c r="F385" s="1" t="s">
-        <v>9</v>
+        <v>463</v>
       </c>
       <c r="G385" s="1" t="s">
         <v>10</v>
@@ -14045,19 +14030,19 @@
         <v>4</v>
       </c>
       <c r="B386" s="1" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="C386" s="1" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="D386" s="1" t="s">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="E386" s="1" t="s">
-        <v>55</v>
+        <v>466</v>
       </c>
       <c r="F386" s="1" t="s">
-        <v>186</v>
+        <v>9</v>
       </c>
       <c r="G386" s="1" t="s">
         <v>10</v>
@@ -14068,16 +14053,16 @@
         <v>4</v>
       </c>
       <c r="B387" s="1" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="C387" s="1" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="D387" s="1" t="s">
         <v>42</v>
       </c>
       <c r="E387" s="1" t="s">
-        <v>237</v>
+        <v>55</v>
       </c>
       <c r="F387" s="1" t="s">
         <v>186</v>
@@ -14091,16 +14076,16 @@
         <v>4</v>
       </c>
       <c r="B388" s="1" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="C388" s="1" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="D388" s="1" t="s">
         <v>42</v>
       </c>
       <c r="E388" s="1" t="s">
-        <v>779</v>
+        <v>237</v>
       </c>
       <c r="F388" s="1" t="s">
         <v>186</v>
@@ -14114,16 +14099,16 @@
         <v>4</v>
       </c>
       <c r="B389" s="1" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="C389" s="1" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="D389" s="1" t="s">
         <v>42</v>
       </c>
       <c r="E389" s="1" t="s">
-        <v>768</v>
+        <v>779</v>
       </c>
       <c r="F389" s="1" t="s">
         <v>186</v>
@@ -14137,16 +14122,16 @@
         <v>4</v>
       </c>
       <c r="B390" s="1" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="C390" s="1" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="D390" s="1" t="s">
         <v>42</v>
       </c>
       <c r="E390" s="1" t="s">
-        <v>1398</v>
+        <v>1532</v>
       </c>
       <c r="F390" s="1" t="s">
         <v>186</v>
@@ -14160,16 +14145,16 @@
         <v>4</v>
       </c>
       <c r="B391" s="1" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="C391" s="1" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="D391" s="1" t="s">
         <v>42</v>
       </c>
       <c r="E391" s="1" t="s">
-        <v>279</v>
+        <v>1396</v>
       </c>
       <c r="F391" s="1" t="s">
         <v>186</v>
@@ -14183,16 +14168,16 @@
         <v>4</v>
       </c>
       <c r="B392" s="1" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="C392" s="1" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="D392" s="1" t="s">
         <v>42</v>
       </c>
       <c r="E392" s="1" t="s">
-        <v>116</v>
+        <v>279</v>
       </c>
       <c r="F392" s="1" t="s">
         <v>186</v>
@@ -14206,16 +14191,16 @@
         <v>4</v>
       </c>
       <c r="B393" s="1" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="C393" s="1" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="D393" s="1" t="s">
         <v>42</v>
       </c>
       <c r="E393" s="1" t="s">
-        <v>242</v>
+        <v>116</v>
       </c>
       <c r="F393" s="1" t="s">
         <v>186</v>
@@ -14229,16 +14214,16 @@
         <v>4</v>
       </c>
       <c r="B394" s="1" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="C394" s="1" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="D394" s="1" t="s">
         <v>42</v>
       </c>
       <c r="E394" s="1" t="s">
-        <v>157</v>
+        <v>115</v>
       </c>
       <c r="F394" s="1" t="s">
         <v>186</v>
@@ -14252,16 +14237,16 @@
         <v>4</v>
       </c>
       <c r="B395" s="1" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="C395" s="1" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="D395" s="1" t="s">
         <v>42</v>
       </c>
       <c r="E395" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F395" s="1" t="s">
         <v>186</v>
@@ -14275,16 +14260,16 @@
         <v>4</v>
       </c>
       <c r="B396" s="1" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="C396" s="1" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="D396" s="1" t="s">
         <v>42</v>
       </c>
       <c r="E396" s="1" t="s">
-        <v>1549</v>
+        <v>160</v>
       </c>
       <c r="F396" s="1" t="s">
         <v>186</v>
@@ -14298,19 +14283,19 @@
         <v>4</v>
       </c>
       <c r="B397" s="1" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="C397" s="1" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="D397" s="1" t="s">
         <v>42</v>
       </c>
       <c r="E397" s="1" t="s">
-        <v>8</v>
+        <v>1555</v>
       </c>
       <c r="F397" s="1" t="s">
-        <v>9</v>
+        <v>186</v>
       </c>
       <c r="G397" s="1" t="s">
         <v>10</v>
@@ -14321,16 +14306,16 @@
         <v>4</v>
       </c>
       <c r="B398" s="1" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="C398" s="1" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="D398" s="1" t="s">
         <v>42</v>
       </c>
       <c r="E398" s="1" t="s">
-        <v>46</v>
+        <v>8</v>
       </c>
       <c r="F398" s="1" t="s">
         <v>9</v>
@@ -14344,16 +14329,16 @@
         <v>4</v>
       </c>
       <c r="B399" s="1" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="C399" s="1" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="D399" s="1" t="s">
         <v>42</v>
       </c>
       <c r="E399" s="1" t="s">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="F399" s="1" t="s">
         <v>9</v>
@@ -14367,16 +14352,16 @@
         <v>4</v>
       </c>
       <c r="B400" s="1" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="C400" s="1" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="D400" s="1" t="s">
         <v>42</v>
       </c>
       <c r="E400" s="1" t="s">
-        <v>8</v>
+        <v>72</v>
       </c>
       <c r="F400" s="1" t="s">
         <v>9</v>
@@ -14390,10 +14375,10 @@
         <v>4</v>
       </c>
       <c r="B401" s="1" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="C401" s="1" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="D401" s="1" t="s">
         <v>42</v>
@@ -14413,16 +14398,16 @@
         <v>4</v>
       </c>
       <c r="B402" s="1" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="C402" s="1" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="D402" s="1" t="s">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="E402" s="1" t="s">
-        <v>242</v>
+        <v>8</v>
       </c>
       <c r="F402" s="1" t="s">
         <v>9</v>
@@ -14436,16 +14421,16 @@
         <v>4</v>
       </c>
       <c r="B403" s="1" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="C403" s="1" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="D403" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E403" s="1" t="s">
-        <v>211</v>
+        <v>55</v>
       </c>
       <c r="F403" s="1" t="s">
         <v>9</v>
@@ -14459,16 +14444,16 @@
         <v>4</v>
       </c>
       <c r="B404" s="1" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="C404" s="1" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="D404" s="1" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E404" s="1" t="s">
-        <v>812</v>
+        <v>211</v>
       </c>
       <c r="F404" s="1" t="s">
         <v>9</v>
@@ -14482,16 +14467,16 @@
         <v>4</v>
       </c>
       <c r="B405" s="1" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="C405" s="1" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="D405" s="1" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E405" s="1" t="s">
-        <v>160</v>
+        <v>812</v>
       </c>
       <c r="F405" s="1" t="s">
         <v>9</v>
@@ -14505,19 +14490,19 @@
         <v>4</v>
       </c>
       <c r="B406" s="1" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="C406" s="1" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="D406" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E406" s="1" t="s">
-        <v>1449</v>
+        <v>160</v>
       </c>
       <c r="F406" s="1" t="s">
-        <v>295</v>
+        <v>9</v>
       </c>
       <c r="G406" s="1" t="s">
         <v>10</v>
@@ -14528,16 +14513,16 @@
         <v>4</v>
       </c>
       <c r="B407" s="1" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C407" s="1" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="D407" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E407" s="1" t="s">
-        <v>1550</v>
+        <v>1444</v>
       </c>
       <c r="F407" s="1" t="s">
         <v>295</v>
@@ -14551,19 +14536,19 @@
         <v>4</v>
       </c>
       <c r="B408" s="1" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="C408" s="1" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="D408" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E408" s="1" t="s">
-        <v>1450</v>
+        <v>173</v>
       </c>
       <c r="F408" s="1" t="s">
-        <v>9</v>
+        <v>295</v>
       </c>
       <c r="G408" s="1" t="s">
         <v>10</v>
@@ -14574,16 +14559,16 @@
         <v>4</v>
       </c>
       <c r="B409" s="1" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="C409" s="1" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="D409" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E409" s="1" t="s">
-        <v>67</v>
+        <v>1445</v>
       </c>
       <c r="F409" s="1" t="s">
         <v>9</v>
@@ -14597,16 +14582,16 @@
         <v>4</v>
       </c>
       <c r="B410" s="1" t="s">
-        <v>1385</v>
+        <v>821</v>
       </c>
       <c r="C410" s="1" t="s">
-        <v>1386</v>
+        <v>822</v>
       </c>
       <c r="D410" s="1" t="s">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="E410" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F410" s="1" t="s">
         <v>9</v>
@@ -14620,16 +14605,16 @@
         <v>4</v>
       </c>
       <c r="B411" s="1" t="s">
-        <v>823</v>
+        <v>1383</v>
       </c>
       <c r="C411" s="1" t="s">
-        <v>824</v>
+        <v>1384</v>
       </c>
       <c r="D411" s="1" t="s">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="E411" s="1" t="s">
-        <v>116</v>
+        <v>64</v>
       </c>
       <c r="F411" s="1" t="s">
         <v>9</v>
@@ -14643,16 +14628,16 @@
         <v>4</v>
       </c>
       <c r="B412" s="1" t="s">
-        <v>1387</v>
+        <v>823</v>
       </c>
       <c r="C412" s="1" t="s">
-        <v>1388</v>
+        <v>824</v>
       </c>
       <c r="D412" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E412" s="1" t="s">
-        <v>1147</v>
+        <v>116</v>
       </c>
       <c r="F412" s="1" t="s">
         <v>9</v>
@@ -14666,16 +14651,16 @@
         <v>4</v>
       </c>
       <c r="B413" s="1" t="s">
-        <v>825</v>
+        <v>1385</v>
       </c>
       <c r="C413" s="1" t="s">
-        <v>826</v>
+        <v>1386</v>
       </c>
       <c r="D413" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E413" s="1" t="s">
-        <v>1551</v>
+        <v>1145</v>
       </c>
       <c r="F413" s="1" t="s">
         <v>9</v>
@@ -14689,16 +14674,16 @@
         <v>4</v>
       </c>
       <c r="B414" s="1" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="C414" s="1" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="D414" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E414" s="1" t="s">
-        <v>1552</v>
+        <v>1556</v>
       </c>
       <c r="F414" s="1" t="s">
         <v>9</v>
@@ -14712,16 +14697,16 @@
         <v>4</v>
       </c>
       <c r="B415" s="1" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="C415" s="1" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="D415" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E415" s="1" t="s">
-        <v>8</v>
+        <v>1557</v>
       </c>
       <c r="F415" s="1" t="s">
         <v>9</v>
@@ -14735,16 +14720,16 @@
         <v>4</v>
       </c>
       <c r="B416" s="1" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="C416" s="1" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="D416" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E416" s="1" t="s">
-        <v>97</v>
+        <v>8</v>
       </c>
       <c r="F416" s="1" t="s">
         <v>9</v>
@@ -14758,16 +14743,16 @@
         <v>4</v>
       </c>
       <c r="B417" s="1" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="C417" s="1" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="D417" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E417" s="1" t="s">
-        <v>8</v>
+        <v>97</v>
       </c>
       <c r="F417" s="1" t="s">
         <v>9</v>
@@ -14781,16 +14766,16 @@
         <v>4</v>
       </c>
       <c r="B418" s="1" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="C418" s="1" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="D418" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E418" s="1" t="s">
-        <v>52</v>
+        <v>8</v>
       </c>
       <c r="F418" s="1" t="s">
         <v>9</v>
@@ -14804,16 +14789,16 @@
         <v>4</v>
       </c>
       <c r="B419" s="1" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="C419" s="1" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="D419" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E419" s="1" t="s">
-        <v>82</v>
+        <v>52</v>
       </c>
       <c r="F419" s="1" t="s">
         <v>9</v>
@@ -14827,16 +14812,16 @@
         <v>4</v>
       </c>
       <c r="B420" s="1" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="C420" s="1" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="D420" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E420" s="1" t="s">
-        <v>263</v>
+        <v>82</v>
       </c>
       <c r="F420" s="1" t="s">
         <v>9</v>
@@ -14850,16 +14835,16 @@
         <v>4</v>
       </c>
       <c r="B421" s="1" t="s">
-        <v>1422</v>
+        <v>839</v>
       </c>
       <c r="C421" s="1" t="s">
-        <v>1423</v>
+        <v>840</v>
       </c>
       <c r="D421" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E421" s="1" t="s">
-        <v>170</v>
+        <v>263</v>
       </c>
       <c r="F421" s="1" t="s">
         <v>9</v>
@@ -14873,16 +14858,16 @@
         <v>4</v>
       </c>
       <c r="B422" s="1" t="s">
-        <v>841</v>
+        <v>1418</v>
       </c>
       <c r="C422" s="1" t="s">
-        <v>842</v>
+        <v>1419</v>
       </c>
       <c r="D422" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E422" s="1" t="s">
-        <v>922</v>
+        <v>46</v>
       </c>
       <c r="F422" s="1" t="s">
         <v>9</v>
@@ -14896,16 +14881,16 @@
         <v>4</v>
       </c>
       <c r="B423" s="1" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="C423" s="1" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="D423" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E423" s="1" t="s">
-        <v>1471</v>
+        <v>921</v>
       </c>
       <c r="F423" s="1" t="s">
         <v>9</v>
@@ -14919,19 +14904,19 @@
         <v>4</v>
       </c>
       <c r="B424" s="1" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="C424" s="1" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="D424" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E424" s="1" t="s">
-        <v>242</v>
+        <v>1466</v>
       </c>
       <c r="F424" s="1" t="s">
-        <v>112</v>
+        <v>9</v>
       </c>
       <c r="G424" s="1" t="s">
         <v>10</v>
@@ -14942,19 +14927,19 @@
         <v>4</v>
       </c>
       <c r="B425" s="1" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="C425" s="1" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="D425" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E425" s="1" t="s">
-        <v>1147</v>
+        <v>242</v>
       </c>
       <c r="F425" s="1" t="s">
-        <v>9</v>
+        <v>112</v>
       </c>
       <c r="G425" s="1" t="s">
         <v>10</v>
@@ -14971,10 +14956,10 @@
         <v>848</v>
       </c>
       <c r="D426" s="1" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E426" s="1" t="s">
-        <v>849</v>
+        <v>1145</v>
       </c>
       <c r="F426" s="1" t="s">
         <v>9</v>
@@ -14988,16 +14973,16 @@
         <v>4</v>
       </c>
       <c r="B427" s="1" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="C427" s="1" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="D427" s="1" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E427" s="1" t="s">
-        <v>1451</v>
+        <v>849</v>
       </c>
       <c r="F427" s="1" t="s">
         <v>9</v>
@@ -15011,16 +14996,16 @@
         <v>4</v>
       </c>
       <c r="B428" s="1" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="C428" s="1" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="D428" s="1" t="s">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="E428" s="1" t="s">
-        <v>160</v>
+        <v>1446</v>
       </c>
       <c r="F428" s="1" t="s">
         <v>9</v>
@@ -15034,16 +15019,16 @@
         <v>4</v>
       </c>
       <c r="B429" s="1" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="C429" s="1" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="D429" s="1" t="s">
         <v>42</v>
       </c>
       <c r="E429" s="1" t="s">
-        <v>1384</v>
+        <v>160</v>
       </c>
       <c r="F429" s="1" t="s">
         <v>9</v>
@@ -15057,16 +15042,16 @@
         <v>4</v>
       </c>
       <c r="B430" s="1" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="C430" s="1" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="D430" s="1" t="s">
         <v>42</v>
       </c>
       <c r="E430" s="1" t="s">
-        <v>274</v>
+        <v>1382</v>
       </c>
       <c r="F430" s="1" t="s">
         <v>9</v>
@@ -15080,16 +15065,16 @@
         <v>4</v>
       </c>
       <c r="B431" s="1" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="C431" s="1" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="D431" s="1" t="s">
         <v>42</v>
       </c>
       <c r="E431" s="1" t="s">
-        <v>1463</v>
+        <v>1558</v>
       </c>
       <c r="F431" s="1" t="s">
         <v>9</v>
@@ -15103,16 +15088,16 @@
         <v>4</v>
       </c>
       <c r="B432" s="1" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="C432" s="1" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="D432" s="1" t="s">
         <v>42</v>
       </c>
       <c r="E432" s="1" t="s">
-        <v>1553</v>
+        <v>1458</v>
       </c>
       <c r="F432" s="1" t="s">
         <v>9</v>
@@ -15126,19 +15111,19 @@
         <v>4</v>
       </c>
       <c r="B433" s="1" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="C433" s="1" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="D433" s="1" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="E433" s="1" t="s">
-        <v>1554</v>
+        <v>1505</v>
       </c>
       <c r="F433" s="1" t="s">
-        <v>463</v>
+        <v>9</v>
       </c>
       <c r="G433" s="1" t="s">
         <v>10</v>
@@ -15149,16 +15134,16 @@
         <v>4</v>
       </c>
       <c r="B434" s="1" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="C434" s="1" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="D434" s="1" t="s">
         <v>33</v>
       </c>
       <c r="E434" s="1" t="s">
-        <v>160</v>
+        <v>1559</v>
       </c>
       <c r="F434" s="1" t="s">
         <v>463</v>
@@ -15172,19 +15157,19 @@
         <v>4</v>
       </c>
       <c r="B435" s="1" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="C435" s="1" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="D435" s="1" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="E435" s="1" t="s">
-        <v>8</v>
+        <v>160</v>
       </c>
       <c r="F435" s="1" t="s">
-        <v>9</v>
+        <v>463</v>
       </c>
       <c r="G435" s="1" t="s">
         <v>10</v>
@@ -15195,16 +15180,16 @@
         <v>4</v>
       </c>
       <c r="B436" s="1" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="C436" s="1" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="D436" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E436" s="1" t="s">
-        <v>72</v>
+        <v>8</v>
       </c>
       <c r="F436" s="1" t="s">
         <v>9</v>
@@ -15218,16 +15203,16 @@
         <v>4</v>
       </c>
       <c r="B437" s="1" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="C437" s="1" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="D437" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E437" s="1" t="s">
-        <v>30</v>
+        <v>72</v>
       </c>
       <c r="F437" s="1" t="s">
         <v>9</v>
@@ -15241,16 +15226,16 @@
         <v>4</v>
       </c>
       <c r="B438" s="1" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="C438" s="1" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="D438" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E438" s="1" t="s">
-        <v>115</v>
+        <v>160</v>
       </c>
       <c r="F438" s="1" t="s">
         <v>9</v>
@@ -15264,16 +15249,16 @@
         <v>4</v>
       </c>
       <c r="B439" s="1" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="C439" s="1" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="D439" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E439" s="1" t="s">
-        <v>43</v>
+        <v>115</v>
       </c>
       <c r="F439" s="1" t="s">
         <v>9</v>
@@ -15287,16 +15272,16 @@
         <v>4</v>
       </c>
       <c r="B440" s="1" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="C440" s="1" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="D440" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E440" s="1" t="s">
-        <v>242</v>
+        <v>43</v>
       </c>
       <c r="F440" s="1" t="s">
         <v>9</v>
@@ -15310,16 +15295,16 @@
         <v>4</v>
       </c>
       <c r="B441" s="1" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="C441" s="1" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="D441" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E441" s="1" t="s">
-        <v>1450</v>
+        <v>242</v>
       </c>
       <c r="F441" s="1" t="s">
         <v>9</v>
@@ -15333,16 +15318,16 @@
         <v>4</v>
       </c>
       <c r="B442" s="1" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="C442" s="1" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="D442" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E442" s="1" t="s">
-        <v>148</v>
+        <v>1491</v>
       </c>
       <c r="F442" s="1" t="s">
         <v>9</v>
@@ -15356,16 +15341,16 @@
         <v>4</v>
       </c>
       <c r="B443" s="1" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="C443" s="1" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="D443" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E443" s="1" t="s">
-        <v>98</v>
+        <v>148</v>
       </c>
       <c r="F443" s="1" t="s">
         <v>9</v>
@@ -15379,16 +15364,16 @@
         <v>4</v>
       </c>
       <c r="B444" s="1" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="C444" s="1" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="D444" s="1" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E444" s="1" t="s">
-        <v>64</v>
+        <v>98</v>
       </c>
       <c r="F444" s="1" t="s">
         <v>9</v>
@@ -15402,16 +15387,16 @@
         <v>4</v>
       </c>
       <c r="B445" s="1" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="C445" s="1" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="D445" s="1" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E445" s="1" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="F445" s="1" t="s">
         <v>9</v>
@@ -15425,16 +15410,16 @@
         <v>4</v>
       </c>
       <c r="B446" s="1" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="C446" s="1" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="D446" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E446" s="1" t="s">
-        <v>94</v>
+        <v>55</v>
       </c>
       <c r="F446" s="1" t="s">
         <v>9</v>
@@ -15448,16 +15433,16 @@
         <v>4</v>
       </c>
       <c r="B447" s="1" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="C447" s="1" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="D447" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E447" s="1" t="s">
-        <v>116</v>
+        <v>349</v>
       </c>
       <c r="F447" s="1" t="s">
         <v>9</v>
@@ -15471,16 +15456,16 @@
         <v>4</v>
       </c>
       <c r="B448" s="1" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="C448" s="1" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="D448" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E448" s="1" t="s">
-        <v>170</v>
+        <v>116</v>
       </c>
       <c r="F448" s="1" t="s">
         <v>9</v>
@@ -15494,16 +15479,16 @@
         <v>4</v>
       </c>
       <c r="B449" s="1" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="C449" s="1" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="D449" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E449" s="1" t="s">
-        <v>896</v>
+        <v>170</v>
       </c>
       <c r="F449" s="1" t="s">
         <v>9</v>
@@ -15517,19 +15502,19 @@
         <v>4</v>
       </c>
       <c r="B450" s="1" t="s">
-        <v>897</v>
+        <v>894</v>
       </c>
       <c r="C450" s="1" t="s">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="D450" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E450" s="1" t="s">
-        <v>899</v>
+        <v>896</v>
       </c>
       <c r="F450" s="1" t="s">
-        <v>112</v>
+        <v>9</v>
       </c>
       <c r="G450" s="1" t="s">
         <v>10</v>
@@ -15540,19 +15525,19 @@
         <v>4</v>
       </c>
       <c r="B451" s="1" t="s">
-        <v>900</v>
+        <v>897</v>
       </c>
       <c r="C451" s="1" t="s">
-        <v>901</v>
+        <v>898</v>
       </c>
       <c r="D451" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E451" s="1" t="s">
-        <v>1555</v>
+        <v>899</v>
       </c>
       <c r="F451" s="1" t="s">
-        <v>9</v>
+        <v>112</v>
       </c>
       <c r="G451" s="1" t="s">
         <v>10</v>
@@ -15563,16 +15548,16 @@
         <v>4</v>
       </c>
       <c r="B452" s="1" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="C452" s="1" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="D452" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E452" s="1" t="s">
-        <v>477</v>
+        <v>1560</v>
       </c>
       <c r="F452" s="1" t="s">
         <v>9</v>
@@ -15586,19 +15571,19 @@
         <v>4</v>
       </c>
       <c r="B453" s="1" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="C453" s="1" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="D453" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E453" s="1" t="s">
-        <v>1452</v>
+        <v>477</v>
       </c>
       <c r="F453" s="1" t="s">
-        <v>112</v>
+        <v>9</v>
       </c>
       <c r="G453" s="1" t="s">
         <v>10</v>
@@ -15609,19 +15594,19 @@
         <v>4</v>
       </c>
       <c r="B454" s="1" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="C454" s="1" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="D454" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E454" s="1" t="s">
-        <v>779</v>
+        <v>1447</v>
       </c>
       <c r="F454" s="1" t="s">
-        <v>9</v>
+        <v>112</v>
       </c>
       <c r="G454" s="1" t="s">
         <v>10</v>
@@ -15632,16 +15617,16 @@
         <v>4</v>
       </c>
       <c r="B455" s="1" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="C455" s="1" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="D455" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E455" s="1" t="s">
-        <v>910</v>
+        <v>779</v>
       </c>
       <c r="F455" s="1" t="s">
         <v>9</v>
@@ -15655,16 +15640,16 @@
         <v>4</v>
       </c>
       <c r="B456" s="1" t="s">
-        <v>911</v>
+        <v>908</v>
       </c>
       <c r="C456" s="1" t="s">
-        <v>912</v>
+        <v>909</v>
       </c>
       <c r="D456" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E456" s="1" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="F456" s="1" t="s">
         <v>9</v>
@@ -15678,16 +15663,16 @@
         <v>4</v>
       </c>
       <c r="B457" s="1" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="C457" s="1" t="s">
-        <v>915</v>
+        <v>912</v>
       </c>
       <c r="D457" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E457" s="1" t="s">
-        <v>1556</v>
+        <v>1561</v>
       </c>
       <c r="F457" s="1" t="s">
         <v>9</v>
@@ -15701,16 +15686,16 @@
         <v>4</v>
       </c>
       <c r="B458" s="1" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="C458" s="1" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="D458" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E458" s="1" t="s">
-        <v>1402</v>
+        <v>1562</v>
       </c>
       <c r="F458" s="1" t="s">
         <v>9</v>
@@ -15724,16 +15709,16 @@
         <v>4</v>
       </c>
       <c r="B459" s="1" t="s">
-        <v>918</v>
+        <v>915</v>
       </c>
       <c r="C459" s="1" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="D459" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E459" s="1" t="s">
-        <v>1511</v>
+        <v>543</v>
       </c>
       <c r="F459" s="1" t="s">
         <v>9</v>
@@ -15747,16 +15732,16 @@
         <v>4</v>
       </c>
       <c r="B460" s="1" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="C460" s="1" t="s">
-        <v>921</v>
+        <v>918</v>
       </c>
       <c r="D460" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E460" s="1" t="s">
-        <v>27</v>
+        <v>1563</v>
       </c>
       <c r="F460" s="1" t="s">
         <v>9</v>
@@ -15770,19 +15755,19 @@
         <v>4</v>
       </c>
       <c r="B461" s="1" t="s">
-        <v>923</v>
+        <v>919</v>
       </c>
       <c r="C461" s="1" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="D461" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E461" s="1" t="s">
-        <v>1476</v>
+        <v>27</v>
       </c>
       <c r="F461" s="1" t="s">
-        <v>112</v>
+        <v>9</v>
       </c>
       <c r="G461" s="1" t="s">
         <v>10</v>
@@ -15793,16 +15778,16 @@
         <v>4</v>
       </c>
       <c r="B462" s="1" t="s">
-        <v>925</v>
+        <v>922</v>
       </c>
       <c r="C462" s="1" t="s">
-        <v>926</v>
+        <v>923</v>
       </c>
       <c r="D462" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E462" s="1" t="s">
-        <v>1557</v>
+        <v>1470</v>
       </c>
       <c r="F462" s="1" t="s">
         <v>112</v>
@@ -15816,19 +15801,19 @@
         <v>4</v>
       </c>
       <c r="B463" s="1" t="s">
-        <v>927</v>
+        <v>924</v>
       </c>
       <c r="C463" s="1" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="D463" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E463" s="1" t="s">
-        <v>170</v>
+        <v>1507</v>
       </c>
       <c r="F463" s="1" t="s">
-        <v>9</v>
+        <v>112</v>
       </c>
       <c r="G463" s="1" t="s">
         <v>10</v>
@@ -15839,16 +15824,16 @@
         <v>4</v>
       </c>
       <c r="B464" s="1" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="C464" s="1" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="D464" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E464" s="1" t="s">
-        <v>768</v>
+        <v>170</v>
       </c>
       <c r="F464" s="1" t="s">
         <v>9</v>
@@ -15862,16 +15847,16 @@
         <v>4</v>
       </c>
       <c r="B465" s="1" t="s">
-        <v>1464</v>
+        <v>928</v>
       </c>
       <c r="C465" s="1" t="s">
-        <v>1465</v>
+        <v>929</v>
       </c>
       <c r="D465" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E465" s="1" t="s">
-        <v>613</v>
+        <v>768</v>
       </c>
       <c r="F465" s="1" t="s">
         <v>9</v>
@@ -15885,16 +15870,16 @@
         <v>4</v>
       </c>
       <c r="B466" s="1" t="s">
-        <v>931</v>
+        <v>1459</v>
       </c>
       <c r="C466" s="1" t="s">
-        <v>932</v>
+        <v>1460</v>
       </c>
       <c r="D466" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E466" s="1" t="s">
-        <v>899</v>
+        <v>613</v>
       </c>
       <c r="F466" s="1" t="s">
         <v>9</v>
@@ -15908,16 +15893,16 @@
         <v>4</v>
       </c>
       <c r="B467" s="1" t="s">
-        <v>933</v>
+        <v>930</v>
       </c>
       <c r="C467" s="1" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
       <c r="D467" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E467" s="1" t="s">
-        <v>779</v>
+        <v>1077</v>
       </c>
       <c r="F467" s="1" t="s">
         <v>9</v>
@@ -15931,16 +15916,16 @@
         <v>4</v>
       </c>
       <c r="B468" s="1" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="C468" s="1" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="D468" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E468" s="1" t="s">
-        <v>1453</v>
+        <v>779</v>
       </c>
       <c r="F468" s="1" t="s">
         <v>9</v>
@@ -15954,16 +15939,16 @@
         <v>4</v>
       </c>
       <c r="B469" s="1" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
       <c r="C469" s="1" t="s">
-        <v>938</v>
+        <v>935</v>
       </c>
       <c r="D469" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E469" s="1" t="s">
-        <v>27</v>
+        <v>1448</v>
       </c>
       <c r="F469" s="1" t="s">
         <v>9</v>
@@ -15977,16 +15962,16 @@
         <v>4</v>
       </c>
       <c r="B470" s="1" t="s">
-        <v>939</v>
+        <v>936</v>
       </c>
       <c r="C470" s="1" t="s">
-        <v>940</v>
+        <v>937</v>
       </c>
       <c r="D470" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E470" s="1" t="s">
-        <v>1401</v>
+        <v>27</v>
       </c>
       <c r="F470" s="1" t="s">
         <v>9</v>
@@ -16000,16 +15985,16 @@
         <v>4</v>
       </c>
       <c r="B471" s="1" t="s">
-        <v>1389</v>
+        <v>938</v>
       </c>
       <c r="C471" s="1" t="s">
-        <v>1390</v>
+        <v>939</v>
       </c>
       <c r="D471" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E471" s="1" t="s">
-        <v>374</v>
+        <v>1342</v>
       </c>
       <c r="F471" s="1" t="s">
         <v>9</v>
@@ -16023,16 +16008,16 @@
         <v>4</v>
       </c>
       <c r="B472" s="1" t="s">
-        <v>942</v>
+        <v>1387</v>
       </c>
       <c r="C472" s="1" t="s">
-        <v>943</v>
+        <v>1388</v>
       </c>
       <c r="D472" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E472" s="1" t="s">
-        <v>8</v>
+        <v>374</v>
       </c>
       <c r="F472" s="1" t="s">
         <v>9</v>
@@ -16046,16 +16031,16 @@
         <v>4</v>
       </c>
       <c r="B473" s="1" t="s">
-        <v>944</v>
+        <v>940</v>
       </c>
       <c r="C473" s="1" t="s">
-        <v>945</v>
+        <v>941</v>
       </c>
       <c r="D473" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E473" s="1" t="s">
-        <v>1191</v>
+        <v>8</v>
       </c>
       <c r="F473" s="1" t="s">
         <v>9</v>
@@ -16069,16 +16054,16 @@
         <v>4</v>
       </c>
       <c r="B474" s="1" t="s">
-        <v>946</v>
+        <v>942</v>
       </c>
       <c r="C474" s="1" t="s">
-        <v>947</v>
+        <v>943</v>
       </c>
       <c r="D474" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E474" s="1" t="s">
-        <v>157</v>
+        <v>1189</v>
       </c>
       <c r="F474" s="1" t="s">
         <v>9</v>
@@ -16092,16 +16077,16 @@
         <v>4</v>
       </c>
       <c r="B475" s="1" t="s">
-        <v>948</v>
+        <v>944</v>
       </c>
       <c r="C475" s="1" t="s">
-        <v>949</v>
+        <v>945</v>
       </c>
       <c r="D475" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E475" s="1" t="s">
-        <v>466</v>
+        <v>8</v>
       </c>
       <c r="F475" s="1" t="s">
         <v>9</v>
@@ -16115,16 +16100,16 @@
         <v>4</v>
       </c>
       <c r="B476" s="1" t="s">
-        <v>950</v>
+        <v>946</v>
       </c>
       <c r="C476" s="1" t="s">
-        <v>951</v>
+        <v>947</v>
       </c>
       <c r="D476" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E476" s="1" t="s">
-        <v>952</v>
+        <v>466</v>
       </c>
       <c r="F476" s="1" t="s">
         <v>9</v>
@@ -16138,16 +16123,16 @@
         <v>4</v>
       </c>
       <c r="B477" s="1" t="s">
-        <v>953</v>
+        <v>948</v>
       </c>
       <c r="C477" s="1" t="s">
-        <v>954</v>
+        <v>949</v>
       </c>
       <c r="D477" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E477" s="1" t="s">
-        <v>1512</v>
+        <v>950</v>
       </c>
       <c r="F477" s="1" t="s">
         <v>9</v>
@@ -16161,16 +16146,16 @@
         <v>4</v>
       </c>
       <c r="B478" s="1" t="s">
-        <v>955</v>
+        <v>951</v>
       </c>
       <c r="C478" s="1" t="s">
-        <v>956</v>
+        <v>952</v>
       </c>
       <c r="D478" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E478" s="1" t="s">
-        <v>1513</v>
+        <v>1495</v>
       </c>
       <c r="F478" s="1" t="s">
         <v>9</v>
@@ -16184,16 +16169,16 @@
         <v>4</v>
       </c>
       <c r="B479" s="1" t="s">
-        <v>957</v>
+        <v>953</v>
       </c>
       <c r="C479" s="1" t="s">
-        <v>958</v>
+        <v>954</v>
       </c>
       <c r="D479" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E479" s="1" t="s">
-        <v>1516</v>
+        <v>1496</v>
       </c>
       <c r="F479" s="1" t="s">
         <v>9</v>
@@ -16207,16 +16192,16 @@
         <v>4</v>
       </c>
       <c r="B480" s="1" t="s">
-        <v>959</v>
+        <v>955</v>
       </c>
       <c r="C480" s="1" t="s">
-        <v>960</v>
+        <v>956</v>
       </c>
       <c r="D480" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E480" s="1" t="s">
-        <v>451</v>
+        <v>1564</v>
       </c>
       <c r="F480" s="1" t="s">
         <v>9</v>
@@ -16230,16 +16215,16 @@
         <v>4</v>
       </c>
       <c r="B481" s="1" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
       <c r="C481" s="1" t="s">
-        <v>962</v>
+        <v>958</v>
       </c>
       <c r="D481" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E481" s="1" t="s">
-        <v>349</v>
+        <v>451</v>
       </c>
       <c r="F481" s="1" t="s">
         <v>9</v>
@@ -16253,16 +16238,16 @@
         <v>4</v>
       </c>
       <c r="B482" s="1" t="s">
-        <v>964</v>
+        <v>959</v>
       </c>
       <c r="C482" s="1" t="s">
-        <v>965</v>
+        <v>960</v>
       </c>
       <c r="D482" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E482" s="1" t="s">
-        <v>1558</v>
+        <v>349</v>
       </c>
       <c r="F482" s="1" t="s">
         <v>9</v>
@@ -16276,16 +16261,16 @@
         <v>4</v>
       </c>
       <c r="B483" s="1" t="s">
-        <v>966</v>
+        <v>962</v>
       </c>
       <c r="C483" s="1" t="s">
-        <v>967</v>
+        <v>963</v>
       </c>
       <c r="D483" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E483" s="1" t="s">
-        <v>968</v>
+        <v>1565</v>
       </c>
       <c r="F483" s="1" t="s">
         <v>9</v>
@@ -16299,16 +16284,16 @@
         <v>4</v>
       </c>
       <c r="B484" s="1" t="s">
-        <v>969</v>
+        <v>964</v>
       </c>
       <c r="C484" s="1" t="s">
-        <v>970</v>
+        <v>965</v>
       </c>
       <c r="D484" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E484" s="1" t="s">
-        <v>1514</v>
+        <v>966</v>
       </c>
       <c r="F484" s="1" t="s">
         <v>9</v>
@@ -16322,16 +16307,16 @@
         <v>4</v>
       </c>
       <c r="B485" s="1" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="C485" s="1" t="s">
-        <v>972</v>
+        <v>968</v>
       </c>
       <c r="D485" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E485" s="1" t="s">
-        <v>1450</v>
+        <v>1566</v>
       </c>
       <c r="F485" s="1" t="s">
         <v>9</v>
@@ -16345,16 +16330,16 @@
         <v>4</v>
       </c>
       <c r="B486" s="1" t="s">
-        <v>973</v>
+        <v>969</v>
       </c>
       <c r="C486" s="1" t="s">
-        <v>974</v>
+        <v>970</v>
       </c>
       <c r="D486" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E486" s="1" t="s">
-        <v>116</v>
+        <v>1445</v>
       </c>
       <c r="F486" s="1" t="s">
         <v>9</v>
@@ -16368,16 +16353,16 @@
         <v>4</v>
       </c>
       <c r="B487" s="1" t="s">
-        <v>975</v>
+        <v>971</v>
       </c>
       <c r="C487" s="1" t="s">
-        <v>976</v>
+        <v>972</v>
       </c>
       <c r="D487" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E487" s="1" t="s">
-        <v>27</v>
+        <v>116</v>
       </c>
       <c r="F487" s="1" t="s">
         <v>9</v>
@@ -16391,16 +16376,16 @@
         <v>4</v>
       </c>
       <c r="B488" s="1" t="s">
-        <v>977</v>
+        <v>973</v>
       </c>
       <c r="C488" s="1" t="s">
-        <v>978</v>
+        <v>974</v>
       </c>
       <c r="D488" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E488" s="1" t="s">
-        <v>148</v>
+        <v>27</v>
       </c>
       <c r="F488" s="1" t="s">
         <v>9</v>
@@ -16414,16 +16399,16 @@
         <v>4</v>
       </c>
       <c r="B489" s="1" t="s">
-        <v>979</v>
+        <v>975</v>
       </c>
       <c r="C489" s="1" t="s">
-        <v>980</v>
+        <v>976</v>
       </c>
       <c r="D489" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E489" s="1" t="s">
-        <v>1559</v>
+        <v>148</v>
       </c>
       <c r="F489" s="1" t="s">
         <v>9</v>
@@ -16437,16 +16422,16 @@
         <v>4</v>
       </c>
       <c r="B490" s="1" t="s">
-        <v>981</v>
+        <v>977</v>
       </c>
       <c r="C490" s="1" t="s">
-        <v>982</v>
+        <v>978</v>
       </c>
       <c r="D490" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E490" s="1" t="s">
-        <v>173</v>
+        <v>1508</v>
       </c>
       <c r="F490" s="1" t="s">
         <v>9</v>
@@ -16460,16 +16445,16 @@
         <v>4</v>
       </c>
       <c r="B491" s="1" t="s">
-        <v>983</v>
+        <v>979</v>
       </c>
       <c r="C491" s="1" t="s">
-        <v>984</v>
+        <v>980</v>
       </c>
       <c r="D491" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E491" s="1" t="s">
-        <v>160</v>
+        <v>279</v>
       </c>
       <c r="F491" s="1" t="s">
         <v>9</v>
@@ -16483,16 +16468,16 @@
         <v>4</v>
       </c>
       <c r="B492" s="1" t="s">
-        <v>985</v>
+        <v>981</v>
       </c>
       <c r="C492" s="1" t="s">
-        <v>986</v>
+        <v>982</v>
       </c>
       <c r="D492" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E492" s="1" t="s">
-        <v>613</v>
+        <v>43</v>
       </c>
       <c r="F492" s="1" t="s">
         <v>9</v>
@@ -16506,16 +16491,16 @@
         <v>4</v>
       </c>
       <c r="B493" s="1" t="s">
-        <v>987</v>
+        <v>983</v>
       </c>
       <c r="C493" s="1" t="s">
-        <v>988</v>
+        <v>984</v>
       </c>
       <c r="D493" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E493" s="1" t="s">
-        <v>72</v>
+        <v>613</v>
       </c>
       <c r="F493" s="1" t="s">
         <v>9</v>
@@ -16529,16 +16514,16 @@
         <v>4</v>
       </c>
       <c r="B494" s="1" t="s">
-        <v>989</v>
+        <v>985</v>
       </c>
       <c r="C494" s="1" t="s">
-        <v>990</v>
+        <v>986</v>
       </c>
       <c r="D494" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E494" s="1" t="s">
-        <v>671</v>
+        <v>72</v>
       </c>
       <c r="F494" s="1" t="s">
         <v>9</v>
@@ -16552,16 +16537,16 @@
         <v>4</v>
       </c>
       <c r="B495" s="1" t="s">
-        <v>991</v>
+        <v>987</v>
       </c>
       <c r="C495" s="1" t="s">
-        <v>992</v>
+        <v>988</v>
       </c>
       <c r="D495" s="1" t="s">
-        <v>401</v>
+        <v>7</v>
       </c>
       <c r="E495" s="1" t="s">
-        <v>141</v>
+        <v>1421</v>
       </c>
       <c r="F495" s="1" t="s">
         <v>9</v>
@@ -16575,19 +16560,19 @@
         <v>4</v>
       </c>
       <c r="B496" s="1" t="s">
-        <v>993</v>
+        <v>989</v>
       </c>
       <c r="C496" s="1" t="s">
-        <v>994</v>
+        <v>990</v>
       </c>
       <c r="D496" s="1" t="s">
-        <v>42</v>
+        <v>401</v>
       </c>
       <c r="E496" s="1" t="s">
-        <v>563</v>
+        <v>141</v>
       </c>
       <c r="F496" s="1" t="s">
-        <v>186</v>
+        <v>9</v>
       </c>
       <c r="G496" s="1" t="s">
         <v>10</v>
@@ -16598,16 +16583,16 @@
         <v>4</v>
       </c>
       <c r="B497" s="1" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="C497" s="1" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="D497" s="1" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="E497" s="1" t="s">
-        <v>451</v>
+        <v>242</v>
       </c>
       <c r="F497" s="1" t="s">
         <v>186</v>
@@ -16621,19 +16606,19 @@
         <v>4</v>
       </c>
       <c r="B498" s="1" t="s">
-        <v>995</v>
+        <v>991</v>
       </c>
       <c r="C498" s="1" t="s">
-        <v>996</v>
+        <v>992</v>
       </c>
       <c r="D498" s="1" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E498" s="1" t="s">
-        <v>55</v>
+        <v>451</v>
       </c>
       <c r="F498" s="1" t="s">
-        <v>9</v>
+        <v>186</v>
       </c>
       <c r="G498" s="1" t="s">
         <v>10</v>
@@ -16644,16 +16629,16 @@
         <v>4</v>
       </c>
       <c r="B499" s="1" t="s">
-        <v>997</v>
+        <v>993</v>
       </c>
       <c r="C499" s="1" t="s">
-        <v>998</v>
+        <v>994</v>
       </c>
       <c r="D499" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E499" s="1" t="s">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="F499" s="1" t="s">
         <v>9</v>
@@ -16667,16 +16652,16 @@
         <v>4</v>
       </c>
       <c r="B500" s="1" t="s">
-        <v>999</v>
+        <v>995</v>
       </c>
       <c r="C500" s="1" t="s">
-        <v>1000</v>
+        <v>996</v>
       </c>
       <c r="D500" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E500" s="1" t="s">
-        <v>1560</v>
+        <v>8</v>
       </c>
       <c r="F500" s="1" t="s">
         <v>9</v>
@@ -16690,16 +16675,16 @@
         <v>4</v>
       </c>
       <c r="B501" s="1" t="s">
-        <v>1001</v>
+        <v>997</v>
       </c>
       <c r="C501" s="1" t="s">
-        <v>1002</v>
+        <v>998</v>
       </c>
       <c r="D501" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E501" s="1" t="s">
-        <v>55</v>
+        <v>173</v>
       </c>
       <c r="F501" s="1" t="s">
         <v>9</v>
@@ -16713,16 +16698,16 @@
         <v>4</v>
       </c>
       <c r="B502" s="1" t="s">
-        <v>1003</v>
+        <v>999</v>
       </c>
       <c r="C502" s="1" t="s">
-        <v>1004</v>
+        <v>1000</v>
       </c>
       <c r="D502" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E502" s="1" t="s">
-        <v>410</v>
+        <v>55</v>
       </c>
       <c r="F502" s="1" t="s">
         <v>9</v>
@@ -16736,16 +16721,16 @@
         <v>4</v>
       </c>
       <c r="B503" s="1" t="s">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="C503" s="1" t="s">
-        <v>1006</v>
+        <v>1002</v>
       </c>
       <c r="D503" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E503" s="1" t="s">
-        <v>37</v>
+        <v>623</v>
       </c>
       <c r="F503" s="1" t="s">
         <v>9</v>
@@ -16759,16 +16744,16 @@
         <v>4</v>
       </c>
       <c r="B504" s="1" t="s">
-        <v>1007</v>
+        <v>1003</v>
       </c>
       <c r="C504" s="1" t="s">
-        <v>1008</v>
+        <v>1004</v>
       </c>
       <c r="D504" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E504" s="1" t="s">
-        <v>1466</v>
+        <v>37</v>
       </c>
       <c r="F504" s="1" t="s">
         <v>9</v>
@@ -16782,16 +16767,16 @@
         <v>4</v>
       </c>
       <c r="B505" s="1" t="s">
-        <v>1009</v>
+        <v>1005</v>
       </c>
       <c r="C505" s="1" t="s">
-        <v>1010</v>
+        <v>1006</v>
       </c>
       <c r="D505" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E505" s="1" t="s">
-        <v>160</v>
+        <v>1461</v>
       </c>
       <c r="F505" s="1" t="s">
         <v>9</v>
@@ -16805,16 +16790,16 @@
         <v>4</v>
       </c>
       <c r="B506" s="1" t="s">
-        <v>1011</v>
+        <v>1007</v>
       </c>
       <c r="C506" s="1" t="s">
-        <v>1012</v>
+        <v>1008</v>
       </c>
       <c r="D506" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E506" s="1" t="s">
-        <v>1553</v>
+        <v>160</v>
       </c>
       <c r="F506" s="1" t="s">
         <v>9</v>
@@ -16828,16 +16813,16 @@
         <v>4</v>
       </c>
       <c r="B507" s="1" t="s">
-        <v>1013</v>
+        <v>1009</v>
       </c>
       <c r="C507" s="1" t="s">
-        <v>1014</v>
+        <v>1010</v>
       </c>
       <c r="D507" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E507" s="1" t="s">
-        <v>46</v>
+        <v>1526</v>
       </c>
       <c r="F507" s="1" t="s">
         <v>9</v>
@@ -16851,16 +16836,16 @@
         <v>4</v>
       </c>
       <c r="B508" s="1" t="s">
-        <v>1015</v>
+        <v>1011</v>
       </c>
       <c r="C508" s="1" t="s">
-        <v>1016</v>
+        <v>1012</v>
       </c>
       <c r="D508" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E508" s="1" t="s">
-        <v>1477</v>
+        <v>8</v>
       </c>
       <c r="F508" s="1" t="s">
         <v>9</v>
@@ -16874,16 +16859,16 @@
         <v>4</v>
       </c>
       <c r="B509" s="1" t="s">
-        <v>1017</v>
+        <v>1013</v>
       </c>
       <c r="C509" s="1" t="s">
-        <v>1018</v>
+        <v>1014</v>
       </c>
       <c r="D509" s="1" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E509" s="1" t="s">
-        <v>387</v>
+        <v>1551</v>
       </c>
       <c r="F509" s="1" t="s">
         <v>9</v>
@@ -16897,16 +16882,16 @@
         <v>4</v>
       </c>
       <c r="B510" s="1" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="C510" s="1" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="D510" s="1" t="s">
-        <v>1019</v>
+        <v>19</v>
       </c>
       <c r="E510" s="1" t="s">
-        <v>115</v>
+        <v>387</v>
       </c>
       <c r="F510" s="1" t="s">
         <v>9</v>
@@ -16920,16 +16905,16 @@
         <v>4</v>
       </c>
       <c r="B511" s="1" t="s">
-        <v>1020</v>
+        <v>1015</v>
       </c>
       <c r="C511" s="1" t="s">
-        <v>1021</v>
+        <v>1016</v>
       </c>
       <c r="D511" s="1" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="E511" s="1" t="s">
-        <v>1457</v>
+        <v>115</v>
       </c>
       <c r="F511" s="1" t="s">
         <v>9</v>
@@ -16943,16 +16928,16 @@
         <v>4</v>
       </c>
       <c r="B512" s="1" t="s">
-        <v>1022</v>
+        <v>1018</v>
       </c>
       <c r="C512" s="1" t="s">
-        <v>1023</v>
+        <v>1019</v>
       </c>
       <c r="D512" s="1" t="s">
-        <v>1024</v>
+        <v>1017</v>
       </c>
       <c r="E512" s="1" t="s">
-        <v>82</v>
+        <v>1567</v>
       </c>
       <c r="F512" s="1" t="s">
         <v>9</v>
@@ -16966,16 +16951,16 @@
         <v>4</v>
       </c>
       <c r="B513" s="1" t="s">
-        <v>1478</v>
+        <v>1020</v>
       </c>
       <c r="C513" s="1" t="s">
-        <v>1479</v>
+        <v>1021</v>
       </c>
       <c r="D513" s="1" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="E513" s="1" t="s">
-        <v>1147</v>
+        <v>64</v>
       </c>
       <c r="F513" s="1" t="s">
         <v>9</v>
@@ -16989,16 +16974,16 @@
         <v>4</v>
       </c>
       <c r="B514" s="1" t="s">
-        <v>1561</v>
+        <v>1471</v>
       </c>
       <c r="C514" s="1" t="s">
-        <v>1562</v>
+        <v>1472</v>
       </c>
       <c r="D514" s="1" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="E514" s="1" t="s">
-        <v>34</v>
+        <v>237</v>
       </c>
       <c r="F514" s="1" t="s">
         <v>9</v>
@@ -17012,16 +16997,16 @@
         <v>4</v>
       </c>
       <c r="B515" s="1" t="s">
-        <v>1404</v>
+        <v>1509</v>
       </c>
       <c r="C515" s="1" t="s">
-        <v>1405</v>
+        <v>1510</v>
       </c>
       <c r="D515" s="1" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="E515" s="1" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="F515" s="1" t="s">
         <v>9</v>
@@ -17035,16 +17020,16 @@
         <v>4</v>
       </c>
       <c r="B516" s="1" t="s">
-        <v>1454</v>
+        <v>1401</v>
       </c>
       <c r="C516" s="1" t="s">
-        <v>1455</v>
+        <v>1402</v>
       </c>
       <c r="D516" s="1" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="E516" s="1" t="s">
-        <v>263</v>
+        <v>220</v>
       </c>
       <c r="F516" s="1" t="s">
         <v>9</v>
@@ -17058,16 +17043,16 @@
         <v>4</v>
       </c>
       <c r="B517" s="1" t="s">
-        <v>1025</v>
+        <v>1449</v>
       </c>
       <c r="C517" s="1" t="s">
-        <v>1026</v>
+        <v>1450</v>
       </c>
       <c r="D517" s="1" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="E517" s="1" t="s">
-        <v>160</v>
+        <v>242</v>
       </c>
       <c r="F517" s="1" t="s">
         <v>9</v>
@@ -17081,16 +17066,16 @@
         <v>4</v>
       </c>
       <c r="B518" s="1" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="C518" s="1" t="s">
-        <v>1028</v>
+        <v>1024</v>
       </c>
       <c r="D518" s="1" t="s">
-        <v>7</v>
+        <v>1022</v>
       </c>
       <c r="E518" s="1" t="s">
-        <v>279</v>
+        <v>160</v>
       </c>
       <c r="F518" s="1" t="s">
         <v>9</v>
@@ -17104,16 +17089,16 @@
         <v>4</v>
       </c>
       <c r="B519" s="1" t="s">
-        <v>1029</v>
+        <v>1025</v>
       </c>
       <c r="C519" s="1" t="s">
-        <v>1030</v>
+        <v>1026</v>
       </c>
       <c r="D519" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E519" s="1" t="s">
-        <v>532</v>
+        <v>279</v>
       </c>
       <c r="F519" s="1" t="s">
         <v>9</v>
@@ -17127,19 +17112,19 @@
         <v>4</v>
       </c>
       <c r="B520" s="1" t="s">
-        <v>1031</v>
+        <v>1027</v>
       </c>
       <c r="C520" s="1" t="s">
-        <v>1032</v>
+        <v>1028</v>
       </c>
       <c r="D520" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E520" s="1" t="s">
-        <v>1033</v>
+        <v>532</v>
       </c>
       <c r="F520" s="1" t="s">
-        <v>112</v>
+        <v>9</v>
       </c>
       <c r="G520" s="1" t="s">
         <v>10</v>
@@ -17150,16 +17135,16 @@
         <v>4</v>
       </c>
       <c r="B521" s="1" t="s">
-        <v>1034</v>
+        <v>1029</v>
       </c>
       <c r="C521" s="1" t="s">
-        <v>1035</v>
+        <v>1030</v>
       </c>
       <c r="D521" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E521" s="1" t="s">
-        <v>1036</v>
+        <v>1031</v>
       </c>
       <c r="F521" s="1" t="s">
         <v>112</v>
@@ -17173,19 +17158,19 @@
         <v>4</v>
       </c>
       <c r="B522" s="1" t="s">
-        <v>1037</v>
+        <v>1032</v>
       </c>
       <c r="C522" s="1" t="s">
-        <v>1038</v>
+        <v>1033</v>
       </c>
       <c r="D522" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E522" s="1" t="s">
-        <v>87</v>
+        <v>1034</v>
       </c>
       <c r="F522" s="1" t="s">
-        <v>9</v>
+        <v>112</v>
       </c>
       <c r="G522" s="1" t="s">
         <v>10</v>
@@ -17196,16 +17181,16 @@
         <v>4</v>
       </c>
       <c r="B523" s="1" t="s">
-        <v>1039</v>
+        <v>1035</v>
       </c>
       <c r="C523" s="1" t="s">
-        <v>1040</v>
+        <v>1036</v>
       </c>
       <c r="D523" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E523" s="1" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="F523" s="1" t="s">
         <v>9</v>
@@ -17219,16 +17204,16 @@
         <v>4</v>
       </c>
       <c r="B524" s="1" t="s">
-        <v>1041</v>
+        <v>1037</v>
       </c>
       <c r="C524" s="1" t="s">
-        <v>1042</v>
+        <v>1038</v>
       </c>
       <c r="D524" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E524" s="1" t="s">
-        <v>1563</v>
+        <v>72</v>
       </c>
       <c r="F524" s="1" t="s">
         <v>9</v>
@@ -17242,16 +17227,16 @@
         <v>4</v>
       </c>
       <c r="B525" s="1" t="s">
-        <v>1043</v>
+        <v>1039</v>
       </c>
       <c r="C525" s="1" t="s">
-        <v>1044</v>
+        <v>1040</v>
       </c>
       <c r="D525" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E525" s="1" t="s">
-        <v>116</v>
+        <v>1568</v>
       </c>
       <c r="F525" s="1" t="s">
         <v>9</v>
@@ -17265,16 +17250,16 @@
         <v>4</v>
       </c>
       <c r="B526" s="1" t="s">
-        <v>1045</v>
+        <v>1041</v>
       </c>
       <c r="C526" s="1" t="s">
-        <v>1046</v>
+        <v>1042</v>
       </c>
       <c r="D526" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E526" s="1" t="s">
-        <v>1564</v>
+        <v>116</v>
       </c>
       <c r="F526" s="1" t="s">
         <v>9</v>
@@ -17288,16 +17273,16 @@
         <v>4</v>
       </c>
       <c r="B527" s="1" t="s">
-        <v>1047</v>
+        <v>1043</v>
       </c>
       <c r="C527" s="1" t="s">
-        <v>1048</v>
+        <v>1044</v>
       </c>
       <c r="D527" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E527" s="1" t="s">
-        <v>1565</v>
+        <v>1569</v>
       </c>
       <c r="F527" s="1" t="s">
         <v>9</v>
@@ -17311,16 +17296,16 @@
         <v>4</v>
       </c>
       <c r="B528" s="1" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="C528" s="1" t="s">
-        <v>1050</v>
+        <v>1046</v>
       </c>
       <c r="D528" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E528" s="1" t="s">
-        <v>18</v>
+        <v>1570</v>
       </c>
       <c r="F528" s="1" t="s">
         <v>9</v>
@@ -17334,16 +17319,16 @@
         <v>4</v>
       </c>
       <c r="B529" s="1" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="C529" s="1" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="D529" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E529" s="1" t="s">
-        <v>941</v>
+        <v>18</v>
       </c>
       <c r="F529" s="1" t="s">
         <v>9</v>
@@ -17357,16 +17342,16 @@
         <v>4</v>
       </c>
       <c r="B530" s="1" t="s">
-        <v>1053</v>
+        <v>1049</v>
       </c>
       <c r="C530" s="1" t="s">
-        <v>1054</v>
+        <v>1050</v>
       </c>
       <c r="D530" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E530" s="1" t="s">
-        <v>1566</v>
+        <v>1515</v>
       </c>
       <c r="F530" s="1" t="s">
         <v>9</v>
@@ -17380,16 +17365,16 @@
         <v>4</v>
       </c>
       <c r="B531" s="1" t="s">
-        <v>1055</v>
+        <v>1051</v>
       </c>
       <c r="C531" s="1" t="s">
-        <v>1056</v>
+        <v>1052</v>
       </c>
       <c r="D531" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E531" s="1" t="s">
-        <v>98</v>
+        <v>1506</v>
       </c>
       <c r="F531" s="1" t="s">
         <v>9</v>
@@ -17403,16 +17388,16 @@
         <v>4</v>
       </c>
       <c r="B532" s="1" t="s">
-        <v>1057</v>
+        <v>1053</v>
       </c>
       <c r="C532" s="1" t="s">
-        <v>1058</v>
+        <v>1054</v>
       </c>
       <c r="D532" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E532" s="1" t="s">
-        <v>1567</v>
+        <v>98</v>
       </c>
       <c r="F532" s="1" t="s">
         <v>9</v>
@@ -17426,16 +17411,16 @@
         <v>4</v>
       </c>
       <c r="B533" s="1" t="s">
-        <v>1059</v>
+        <v>1055</v>
       </c>
       <c r="C533" s="1" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="D533" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E533" s="1" t="s">
-        <v>1517</v>
+        <v>1480</v>
       </c>
       <c r="F533" s="1" t="s">
         <v>9</v>
@@ -17449,16 +17434,16 @@
         <v>4</v>
       </c>
       <c r="B534" s="1" t="s">
-        <v>1061</v>
+        <v>1057</v>
       </c>
       <c r="C534" s="1" t="s">
-        <v>1062</v>
+        <v>1058</v>
       </c>
       <c r="D534" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E534" s="1" t="s">
-        <v>306</v>
+        <v>1571</v>
       </c>
       <c r="F534" s="1" t="s">
         <v>9</v>
@@ -17472,16 +17457,16 @@
         <v>4</v>
       </c>
       <c r="B535" s="1" t="s">
-        <v>1063</v>
+        <v>1059</v>
       </c>
       <c r="C535" s="1" t="s">
-        <v>1064</v>
+        <v>1060</v>
       </c>
       <c r="D535" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E535" s="1" t="s">
-        <v>1456</v>
+        <v>306</v>
       </c>
       <c r="F535" s="1" t="s">
         <v>9</v>
@@ -17495,19 +17480,19 @@
         <v>4</v>
       </c>
       <c r="B536" s="1" t="s">
-        <v>1065</v>
+        <v>1061</v>
       </c>
       <c r="C536" s="1" t="s">
-        <v>1066</v>
+        <v>1062</v>
       </c>
       <c r="D536" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E536" s="1" t="s">
-        <v>1457</v>
+        <v>1451</v>
       </c>
       <c r="F536" s="1" t="s">
-        <v>112</v>
+        <v>9</v>
       </c>
       <c r="G536" s="1" t="s">
         <v>10</v>
@@ -17518,19 +17503,19 @@
         <v>4</v>
       </c>
       <c r="B537" s="1" t="s">
-        <v>1067</v>
+        <v>1063</v>
       </c>
       <c r="C537" s="1" t="s">
-        <v>1068</v>
+        <v>1064</v>
       </c>
       <c r="D537" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E537" s="1" t="s">
-        <v>1412</v>
+        <v>1452</v>
       </c>
       <c r="F537" s="1" t="s">
-        <v>9</v>
+        <v>112</v>
       </c>
       <c r="G537" s="1" t="s">
         <v>10</v>
@@ -17541,16 +17526,16 @@
         <v>4</v>
       </c>
       <c r="B538" s="1" t="s">
-        <v>1069</v>
+        <v>1065</v>
       </c>
       <c r="C538" s="1" t="s">
-        <v>1070</v>
+        <v>1066</v>
       </c>
       <c r="D538" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E538" s="1" t="s">
-        <v>82</v>
+        <v>1572</v>
       </c>
       <c r="F538" s="1" t="s">
         <v>9</v>
@@ -17564,16 +17549,16 @@
         <v>4</v>
       </c>
       <c r="B539" s="1" t="s">
-        <v>1071</v>
+        <v>1067</v>
       </c>
       <c r="C539" s="1" t="s">
-        <v>1072</v>
+        <v>1068</v>
       </c>
       <c r="D539" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E539" s="1" t="s">
-        <v>18</v>
+        <v>82</v>
       </c>
       <c r="F539" s="1" t="s">
         <v>9</v>
@@ -17587,16 +17572,16 @@
         <v>4</v>
       </c>
       <c r="B540" s="1" t="s">
-        <v>1073</v>
+        <v>1069</v>
       </c>
       <c r="C540" s="1" t="s">
-        <v>1074</v>
+        <v>1070</v>
       </c>
       <c r="D540" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E540" s="1" t="s">
-        <v>170</v>
+        <v>18</v>
       </c>
       <c r="F540" s="1" t="s">
         <v>9</v>
@@ -17610,16 +17595,16 @@
         <v>4</v>
       </c>
       <c r="B541" s="1" t="s">
-        <v>1075</v>
+        <v>1071</v>
       </c>
       <c r="C541" s="1" t="s">
-        <v>1076</v>
+        <v>1072</v>
       </c>
       <c r="D541" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E541" s="1" t="s">
-        <v>963</v>
+        <v>170</v>
       </c>
       <c r="F541" s="1" t="s">
         <v>9</v>
@@ -17633,16 +17618,16 @@
         <v>4</v>
       </c>
       <c r="B542" s="1" t="s">
-        <v>1077</v>
+        <v>1073</v>
       </c>
       <c r="C542" s="1" t="s">
-        <v>1078</v>
+        <v>1074</v>
       </c>
       <c r="D542" s="1" t="s">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="E542" s="1" t="s">
-        <v>1463</v>
+        <v>961</v>
       </c>
       <c r="F542" s="1" t="s">
         <v>9</v>
@@ -17656,16 +17641,16 @@
         <v>4</v>
       </c>
       <c r="B543" s="1" t="s">
-        <v>1080</v>
+        <v>1075</v>
       </c>
       <c r="C543" s="1" t="s">
-        <v>1081</v>
+        <v>1076</v>
       </c>
       <c r="D543" s="1" t="s">
         <v>42</v>
       </c>
       <c r="E543" s="1" t="s">
-        <v>67</v>
+        <v>1573</v>
       </c>
       <c r="F543" s="1" t="s">
         <v>9</v>
@@ -17679,16 +17664,16 @@
         <v>4</v>
       </c>
       <c r="B544" s="1" t="s">
-        <v>1082</v>
+        <v>1078</v>
       </c>
       <c r="C544" s="1" t="s">
-        <v>1083</v>
+        <v>1079</v>
       </c>
       <c r="D544" s="1" t="s">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="E544" s="1" t="s">
-        <v>8</v>
+        <v>67</v>
       </c>
       <c r="F544" s="1" t="s">
         <v>9</v>
@@ -17702,16 +17687,16 @@
         <v>4</v>
       </c>
       <c r="B545" s="1" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="C545" s="1" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="D545" s="1" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E545" s="1" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="F545" s="1" t="s">
         <v>9</v>
@@ -17725,16 +17710,16 @@
         <v>4</v>
       </c>
       <c r="B546" s="1" t="s">
-        <v>1084</v>
+        <v>1080</v>
       </c>
       <c r="C546" s="1" t="s">
-        <v>1085</v>
+        <v>1081</v>
       </c>
       <c r="D546" s="1" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="E546" s="1" t="s">
-        <v>157</v>
+        <v>37</v>
       </c>
       <c r="F546" s="1" t="s">
         <v>9</v>
@@ -17748,16 +17733,16 @@
         <v>4</v>
       </c>
       <c r="B547" s="1" t="s">
-        <v>1086</v>
+        <v>1082</v>
       </c>
       <c r="C547" s="1" t="s">
-        <v>1087</v>
+        <v>1083</v>
       </c>
       <c r="D547" s="1" t="s">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="E547" s="1" t="s">
-        <v>64</v>
+        <v>157</v>
       </c>
       <c r="F547" s="1" t="s">
         <v>9</v>
@@ -17771,13 +17756,13 @@
         <v>4</v>
       </c>
       <c r="B548" s="1" t="s">
-        <v>1088</v>
+        <v>1084</v>
       </c>
       <c r="C548" s="1" t="s">
-        <v>1089</v>
+        <v>1085</v>
       </c>
       <c r="D548" s="1" t="s">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="E548" s="1" t="s">
         <v>64</v>
@@ -17794,19 +17779,19 @@
         <v>4</v>
       </c>
       <c r="B549" s="1" t="s">
-        <v>1090</v>
+        <v>1086</v>
       </c>
       <c r="C549" s="1" t="s">
-        <v>1091</v>
+        <v>1087</v>
       </c>
       <c r="D549" s="1" t="s">
-        <v>462</v>
+        <v>42</v>
       </c>
       <c r="E549" s="1" t="s">
-        <v>1518</v>
+        <v>64</v>
       </c>
       <c r="F549" s="1" t="s">
-        <v>463</v>
+        <v>9</v>
       </c>
       <c r="G549" s="1" t="s">
         <v>10</v>
@@ -17817,19 +17802,19 @@
         <v>4</v>
       </c>
       <c r="B550" s="1" t="s">
-        <v>1092</v>
+        <v>1088</v>
       </c>
       <c r="C550" s="1" t="s">
-        <v>1093</v>
+        <v>1089</v>
       </c>
       <c r="D550" s="1" t="s">
-        <v>7</v>
+        <v>462</v>
       </c>
       <c r="E550" s="1" t="s">
-        <v>1568</v>
+        <v>1498</v>
       </c>
       <c r="F550" s="1" t="s">
-        <v>9</v>
+        <v>463</v>
       </c>
       <c r="G550" s="1" t="s">
         <v>10</v>
@@ -17840,16 +17825,16 @@
         <v>4</v>
       </c>
       <c r="B551" s="1" t="s">
-        <v>1094</v>
+        <v>1090</v>
       </c>
       <c r="C551" s="1" t="s">
-        <v>1095</v>
+        <v>1091</v>
       </c>
       <c r="D551" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E551" s="1" t="s">
-        <v>27</v>
+        <v>1574</v>
       </c>
       <c r="F551" s="1" t="s">
         <v>9</v>
@@ -17863,16 +17848,16 @@
         <v>4</v>
       </c>
       <c r="B552" s="1" t="s">
-        <v>1096</v>
+        <v>1092</v>
       </c>
       <c r="C552" s="1" t="s">
-        <v>1097</v>
+        <v>1093</v>
       </c>
       <c r="D552" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E552" s="1" t="s">
-        <v>94</v>
+        <v>27</v>
       </c>
       <c r="F552" s="1" t="s">
         <v>9</v>
@@ -17886,16 +17871,16 @@
         <v>4</v>
       </c>
       <c r="B553" s="1" t="s">
-        <v>1098</v>
+        <v>1094</v>
       </c>
       <c r="C553" s="1" t="s">
-        <v>1099</v>
+        <v>1095</v>
       </c>
       <c r="D553" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E553" s="1" t="s">
-        <v>1191</v>
+        <v>94</v>
       </c>
       <c r="F553" s="1" t="s">
         <v>9</v>
@@ -17909,16 +17894,16 @@
         <v>4</v>
       </c>
       <c r="B554" s="1" t="s">
-        <v>1101</v>
+        <v>1096</v>
       </c>
       <c r="C554" s="1" t="s">
-        <v>1102</v>
+        <v>1097</v>
       </c>
       <c r="D554" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E554" s="1" t="s">
-        <v>18</v>
+        <v>1189</v>
       </c>
       <c r="F554" s="1" t="s">
         <v>9</v>
@@ -17932,16 +17917,16 @@
         <v>4</v>
       </c>
       <c r="B555" s="1" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="C555" s="1" t="s">
-        <v>1104</v>
+        <v>1100</v>
       </c>
       <c r="D555" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E555" s="1" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="F555" s="1" t="s">
         <v>9</v>
@@ -17955,19 +17940,19 @@
         <v>4</v>
       </c>
       <c r="B556" s="1" t="s">
-        <v>1105</v>
+        <v>1101</v>
       </c>
       <c r="C556" s="1" t="s">
-        <v>1106</v>
+        <v>1102</v>
       </c>
       <c r="D556" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E556" s="1" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="F556" s="1" t="s">
-        <v>112</v>
+        <v>9</v>
       </c>
       <c r="G556" s="1" t="s">
         <v>10</v>
@@ -17978,19 +17963,19 @@
         <v>4</v>
       </c>
       <c r="B557" s="1" t="s">
-        <v>1107</v>
+        <v>1103</v>
       </c>
       <c r="C557" s="1" t="s">
-        <v>1108</v>
+        <v>1104</v>
       </c>
       <c r="D557" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E557" s="1" t="s">
-        <v>1079</v>
+        <v>46</v>
       </c>
       <c r="F557" s="1" t="s">
-        <v>9</v>
+        <v>112</v>
       </c>
       <c r="G557" s="1" t="s">
         <v>10</v>
@@ -18001,16 +17986,16 @@
         <v>4</v>
       </c>
       <c r="B558" s="1" t="s">
-        <v>1109</v>
+        <v>1105</v>
       </c>
       <c r="C558" s="1" t="s">
-        <v>1110</v>
+        <v>1106</v>
       </c>
       <c r="D558" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E558" s="1" t="s">
-        <v>242</v>
+        <v>1077</v>
       </c>
       <c r="F558" s="1" t="s">
         <v>9</v>
@@ -18024,16 +18009,16 @@
         <v>4</v>
       </c>
       <c r="B559" s="1" t="s">
-        <v>1111</v>
+        <v>1107</v>
       </c>
       <c r="C559" s="1" t="s">
-        <v>1112</v>
+        <v>1108</v>
       </c>
       <c r="D559" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E559" s="1" t="s">
-        <v>1100</v>
+        <v>242</v>
       </c>
       <c r="F559" s="1" t="s">
         <v>9</v>
@@ -18047,16 +18032,16 @@
         <v>4</v>
       </c>
       <c r="B560" s="1" t="s">
-        <v>1113</v>
+        <v>1109</v>
       </c>
       <c r="C560" s="1" t="s">
-        <v>1114</v>
+        <v>1110</v>
       </c>
       <c r="D560" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E560" s="1" t="s">
-        <v>324</v>
+        <v>1098</v>
       </c>
       <c r="F560" s="1" t="s">
         <v>9</v>
@@ -18070,16 +18055,16 @@
         <v>4</v>
       </c>
       <c r="B561" s="1" t="s">
-        <v>1115</v>
+        <v>1111</v>
       </c>
       <c r="C561" s="1" t="s">
-        <v>1116</v>
+        <v>1112</v>
       </c>
       <c r="D561" s="1" t="s">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="E561" s="1" t="s">
-        <v>72</v>
+        <v>324</v>
       </c>
       <c r="F561" s="1" t="s">
         <v>9</v>
@@ -18093,16 +18078,16 @@
         <v>4</v>
       </c>
       <c r="B562" s="1" t="s">
-        <v>1117</v>
+        <v>1113</v>
       </c>
       <c r="C562" s="1" t="s">
-        <v>1118</v>
+        <v>1114</v>
       </c>
       <c r="D562" s="1" t="s">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="E562" s="1" t="s">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="F562" s="1" t="s">
         <v>9</v>
@@ -18116,16 +18101,16 @@
         <v>4</v>
       </c>
       <c r="B563" s="1" t="s">
-        <v>1119</v>
+        <v>1115</v>
       </c>
       <c r="C563" s="1" t="s">
-        <v>1120</v>
+        <v>1116</v>
       </c>
       <c r="D563" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E563" s="1" t="s">
-        <v>124</v>
+        <v>34</v>
       </c>
       <c r="F563" s="1" t="s">
         <v>9</v>
@@ -18139,19 +18124,19 @@
         <v>4</v>
       </c>
       <c r="B564" s="1" t="s">
-        <v>1121</v>
+        <v>1117</v>
       </c>
       <c r="C564" s="1" t="s">
-        <v>1122</v>
+        <v>1118</v>
       </c>
       <c r="D564" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E564" s="1" t="s">
-        <v>1569</v>
+        <v>124</v>
       </c>
       <c r="F564" s="1" t="s">
-        <v>112</v>
+        <v>9</v>
       </c>
       <c r="G564" s="1" t="s">
         <v>10</v>
@@ -18162,19 +18147,19 @@
         <v>4</v>
       </c>
       <c r="B565" s="1" t="s">
-        <v>1123</v>
+        <v>1119</v>
       </c>
       <c r="C565" s="1" t="s">
-        <v>1124</v>
+        <v>1120</v>
       </c>
       <c r="D565" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E565" s="1" t="s">
-        <v>324</v>
+        <v>1511</v>
       </c>
       <c r="F565" s="1" t="s">
-        <v>9</v>
+        <v>112</v>
       </c>
       <c r="G565" s="1" t="s">
         <v>10</v>
@@ -18185,16 +18170,16 @@
         <v>4</v>
       </c>
       <c r="B566" s="1" t="s">
-        <v>1125</v>
+        <v>1121</v>
       </c>
       <c r="C566" s="1" t="s">
-        <v>1126</v>
+        <v>1122</v>
       </c>
       <c r="D566" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E566" s="1" t="s">
-        <v>410</v>
+        <v>324</v>
       </c>
       <c r="F566" s="1" t="s">
         <v>9</v>
@@ -18208,16 +18193,16 @@
         <v>4</v>
       </c>
       <c r="B567" s="1" t="s">
-        <v>1127</v>
+        <v>1123</v>
       </c>
       <c r="C567" s="1" t="s">
-        <v>1128</v>
+        <v>1124</v>
       </c>
       <c r="D567" s="1" t="s">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="E567" s="1" t="s">
-        <v>160</v>
+        <v>410</v>
       </c>
       <c r="F567" s="1" t="s">
         <v>9</v>
@@ -18231,16 +18216,16 @@
         <v>4</v>
       </c>
       <c r="B568" s="1" t="s">
-        <v>1129</v>
+        <v>1125</v>
       </c>
       <c r="C568" s="1" t="s">
-        <v>1130</v>
+        <v>1126</v>
       </c>
       <c r="D568" s="1" t="s">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="E568" s="1" t="s">
-        <v>658</v>
+        <v>160</v>
       </c>
       <c r="F568" s="1" t="s">
         <v>9</v>
@@ -18254,16 +18239,16 @@
         <v>4</v>
       </c>
       <c r="B569" s="1" t="s">
-        <v>1129</v>
+        <v>1127</v>
       </c>
       <c r="C569" s="1" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="D569" s="1" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E569" s="1" t="s">
-        <v>1406</v>
+        <v>279</v>
       </c>
       <c r="F569" s="1" t="s">
         <v>9</v>
@@ -18277,16 +18262,16 @@
         <v>4</v>
       </c>
       <c r="B570" s="1" t="s">
-        <v>1131</v>
+        <v>1127</v>
       </c>
       <c r="C570" s="1" t="s">
-        <v>1132</v>
+        <v>1128</v>
       </c>
       <c r="D570" s="1" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E570" s="1" t="s">
-        <v>543</v>
+        <v>1403</v>
       </c>
       <c r="F570" s="1" t="s">
         <v>9</v>
@@ -18300,16 +18285,16 @@
         <v>4</v>
       </c>
       <c r="B571" s="1" t="s">
-        <v>1133</v>
+        <v>1129</v>
       </c>
       <c r="C571" s="1" t="s">
-        <v>1134</v>
+        <v>1130</v>
       </c>
       <c r="D571" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E571" s="1" t="s">
-        <v>374</v>
+        <v>1515</v>
       </c>
       <c r="F571" s="1" t="s">
         <v>9</v>
@@ -18323,16 +18308,16 @@
         <v>4</v>
       </c>
       <c r="B572" s="1" t="s">
-        <v>1135</v>
+        <v>1131</v>
       </c>
       <c r="C572" s="1" t="s">
-        <v>1136</v>
+        <v>1132</v>
       </c>
       <c r="D572" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E572" s="1" t="s">
-        <v>46</v>
+        <v>1473</v>
       </c>
       <c r="F572" s="1" t="s">
         <v>9</v>
@@ -18346,16 +18331,16 @@
         <v>4</v>
       </c>
       <c r="B573" s="1" t="s">
-        <v>1137</v>
+        <v>1133</v>
       </c>
       <c r="C573" s="1" t="s">
-        <v>1138</v>
+        <v>1134</v>
       </c>
       <c r="D573" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E573" s="1" t="s">
-        <v>622</v>
+        <v>46</v>
       </c>
       <c r="F573" s="1" t="s">
         <v>9</v>
@@ -18369,10 +18354,10 @@
         <v>4</v>
       </c>
       <c r="B574" s="1" t="s">
-        <v>1139</v>
+        <v>1135</v>
       </c>
       <c r="C574" s="1" t="s">
-        <v>1140</v>
+        <v>1136</v>
       </c>
       <c r="D574" s="1" t="s">
         <v>7</v>
@@ -18392,16 +18377,16 @@
         <v>4</v>
       </c>
       <c r="B575" s="1" t="s">
-        <v>1141</v>
+        <v>1137</v>
       </c>
       <c r="C575" s="1" t="s">
-        <v>1142</v>
+        <v>1138</v>
       </c>
       <c r="D575" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E575" s="1" t="s">
-        <v>1515</v>
+        <v>622</v>
       </c>
       <c r="F575" s="1" t="s">
         <v>9</v>
@@ -18415,16 +18400,16 @@
         <v>4</v>
       </c>
       <c r="B576" s="1" t="s">
-        <v>1143</v>
+        <v>1139</v>
       </c>
       <c r="C576" s="1" t="s">
-        <v>1144</v>
+        <v>1140</v>
       </c>
       <c r="D576" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E576" s="1" t="s">
-        <v>922</v>
+        <v>173</v>
       </c>
       <c r="F576" s="1" t="s">
         <v>9</v>
@@ -18438,16 +18423,16 @@
         <v>4</v>
       </c>
       <c r="B577" s="1" t="s">
-        <v>1145</v>
+        <v>1141</v>
       </c>
       <c r="C577" s="1" t="s">
-        <v>1146</v>
+        <v>1142</v>
       </c>
       <c r="D577" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E577" s="1" t="s">
-        <v>1147</v>
+        <v>97</v>
       </c>
       <c r="F577" s="1" t="s">
         <v>9</v>
@@ -18461,16 +18446,16 @@
         <v>4</v>
       </c>
       <c r="B578" s="1" t="s">
-        <v>1148</v>
+        <v>1143</v>
       </c>
       <c r="C578" s="1" t="s">
-        <v>1149</v>
+        <v>1144</v>
       </c>
       <c r="D578" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E578" s="1" t="s">
-        <v>1426</v>
+        <v>1145</v>
       </c>
       <c r="F578" s="1" t="s">
         <v>9</v>
@@ -18484,16 +18469,16 @@
         <v>4</v>
       </c>
       <c r="B579" s="1" t="s">
-        <v>1150</v>
+        <v>1146</v>
       </c>
       <c r="C579" s="1" t="s">
-        <v>1151</v>
+        <v>1147</v>
       </c>
       <c r="D579" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E579" s="1" t="s">
-        <v>18</v>
+        <v>1499</v>
       </c>
       <c r="F579" s="1" t="s">
         <v>9</v>
@@ -18507,19 +18492,19 @@
         <v>4</v>
       </c>
       <c r="B580" s="1" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="C580" s="1" t="s">
-        <v>1153</v>
+        <v>1149</v>
       </c>
       <c r="D580" s="1" t="s">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="E580" s="1" t="s">
-        <v>72</v>
+        <v>18</v>
       </c>
       <c r="F580" s="1" t="s">
-        <v>186</v>
+        <v>9</v>
       </c>
       <c r="G580" s="1" t="s">
         <v>10</v>
@@ -18530,16 +18515,16 @@
         <v>4</v>
       </c>
       <c r="B581" s="1" t="s">
-        <v>1154</v>
+        <v>1150</v>
       </c>
       <c r="C581" s="1" t="s">
-        <v>1155</v>
+        <v>1151</v>
       </c>
       <c r="D581" s="1" t="s">
         <v>42</v>
       </c>
       <c r="E581" s="1" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="F581" s="1" t="s">
         <v>186</v>
@@ -18553,16 +18538,16 @@
         <v>4</v>
       </c>
       <c r="B582" s="1" t="s">
-        <v>1156</v>
+        <v>1152</v>
       </c>
       <c r="C582" s="1" t="s">
-        <v>1157</v>
+        <v>1153</v>
       </c>
       <c r="D582" s="1" t="s">
         <v>42</v>
       </c>
       <c r="E582" s="1" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="F582" s="1" t="s">
         <v>186</v>
@@ -18576,19 +18561,19 @@
         <v>4</v>
       </c>
       <c r="B583" s="1" t="s">
-        <v>1158</v>
+        <v>1154</v>
       </c>
       <c r="C583" s="1" t="s">
-        <v>1159</v>
+        <v>1155</v>
       </c>
       <c r="D583" s="1" t="s">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="E583" s="1" t="s">
-        <v>1160</v>
+        <v>72</v>
       </c>
       <c r="F583" s="1" t="s">
-        <v>9</v>
+        <v>186</v>
       </c>
       <c r="G583" s="1" t="s">
         <v>10</v>
@@ -18599,16 +18584,16 @@
         <v>4</v>
       </c>
       <c r="B584" s="1" t="s">
-        <v>1161</v>
+        <v>1156</v>
       </c>
       <c r="C584" s="1" t="s">
-        <v>1162</v>
+        <v>1157</v>
       </c>
       <c r="D584" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E584" s="1" t="s">
-        <v>148</v>
+        <v>1158</v>
       </c>
       <c r="F584" s="1" t="s">
         <v>9</v>
@@ -18622,19 +18607,19 @@
         <v>4</v>
       </c>
       <c r="B585" s="1" t="s">
-        <v>1163</v>
+        <v>1159</v>
       </c>
       <c r="C585" s="1" t="s">
-        <v>1164</v>
+        <v>1160</v>
       </c>
       <c r="D585" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E585" s="1" t="s">
-        <v>64</v>
+        <v>148</v>
       </c>
       <c r="F585" s="1" t="s">
-        <v>112</v>
+        <v>9</v>
       </c>
       <c r="G585" s="1" t="s">
         <v>10</v>
@@ -18645,19 +18630,19 @@
         <v>4</v>
       </c>
       <c r="B586" s="1" t="s">
-        <v>1165</v>
+        <v>1161</v>
       </c>
       <c r="C586" s="1" t="s">
-        <v>1166</v>
+        <v>1162</v>
       </c>
       <c r="D586" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E586" s="1" t="s">
-        <v>8</v>
+        <v>64</v>
       </c>
       <c r="F586" s="1" t="s">
-        <v>9</v>
+        <v>112</v>
       </c>
       <c r="G586" s="1" t="s">
         <v>10</v>
@@ -18668,16 +18653,16 @@
         <v>4</v>
       </c>
       <c r="B587" s="1" t="s">
-        <v>1167</v>
+        <v>1163</v>
       </c>
       <c r="C587" s="1" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="D587" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E587" s="1" t="s">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="F587" s="1" t="s">
         <v>9</v>
@@ -18691,16 +18676,16 @@
         <v>4</v>
       </c>
       <c r="B588" s="1" t="s">
-        <v>1169</v>
+        <v>1165</v>
       </c>
       <c r="C588" s="1" t="s">
-        <v>1170</v>
+        <v>1166</v>
       </c>
       <c r="D588" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E588" s="1" t="s">
-        <v>157</v>
+        <v>43</v>
       </c>
       <c r="F588" s="1" t="s">
         <v>9</v>
@@ -18714,16 +18699,16 @@
         <v>4</v>
       </c>
       <c r="B589" s="1" t="s">
-        <v>1171</v>
+        <v>1167</v>
       </c>
       <c r="C589" s="1" t="s">
-        <v>1172</v>
+        <v>1168</v>
       </c>
       <c r="D589" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E589" s="1" t="s">
-        <v>43</v>
+        <v>157</v>
       </c>
       <c r="F589" s="1" t="s">
         <v>9</v>
@@ -18737,16 +18722,16 @@
         <v>4</v>
       </c>
       <c r="B590" s="1" t="s">
-        <v>1173</v>
+        <v>1169</v>
       </c>
       <c r="C590" s="1" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
       <c r="D590" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E590" s="1" t="s">
-        <v>170</v>
+        <v>43</v>
       </c>
       <c r="F590" s="1" t="s">
         <v>9</v>
@@ -18760,16 +18745,16 @@
         <v>4</v>
       </c>
       <c r="B591" s="1" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="C591" s="1" t="s">
-        <v>1176</v>
+        <v>1172</v>
       </c>
       <c r="D591" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E591" s="1" t="s">
-        <v>263</v>
+        <v>170</v>
       </c>
       <c r="F591" s="1" t="s">
         <v>9</v>
@@ -18783,16 +18768,16 @@
         <v>4</v>
       </c>
       <c r="B592" s="1" t="s">
-        <v>1177</v>
+        <v>1173</v>
       </c>
       <c r="C592" s="1" t="s">
-        <v>1178</v>
+        <v>1174</v>
       </c>
       <c r="D592" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E592" s="1" t="s">
-        <v>543</v>
+        <v>263</v>
       </c>
       <c r="F592" s="1" t="s">
         <v>9</v>
@@ -18806,16 +18791,16 @@
         <v>4</v>
       </c>
       <c r="B593" s="1" t="s">
-        <v>1179</v>
+        <v>1175</v>
       </c>
       <c r="C593" s="1" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="D593" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E593" s="1" t="s">
-        <v>46</v>
+        <v>543</v>
       </c>
       <c r="F593" s="1" t="s">
         <v>9</v>
@@ -18829,16 +18814,16 @@
         <v>4</v>
       </c>
       <c r="B594" s="1" t="s">
-        <v>1181</v>
+        <v>1177</v>
       </c>
       <c r="C594" s="1" t="s">
-        <v>1182</v>
+        <v>1178</v>
       </c>
       <c r="D594" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E594" s="1" t="s">
-        <v>148</v>
+        <v>46</v>
       </c>
       <c r="F594" s="1" t="s">
         <v>9</v>
@@ -18852,16 +18837,16 @@
         <v>4</v>
       </c>
       <c r="B595" s="1" t="s">
-        <v>1183</v>
+        <v>1179</v>
       </c>
       <c r="C595" s="1" t="s">
-        <v>1184</v>
+        <v>1180</v>
       </c>
       <c r="D595" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E595" s="1" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="F595" s="1" t="s">
         <v>9</v>
@@ -18875,16 +18860,16 @@
         <v>4</v>
       </c>
       <c r="B596" s="1" t="s">
-        <v>1185</v>
+        <v>1181</v>
       </c>
       <c r="C596" s="1" t="s">
-        <v>1186</v>
+        <v>1182</v>
       </c>
       <c r="D596" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E596" s="1" t="s">
-        <v>8</v>
+        <v>121</v>
       </c>
       <c r="F596" s="1" t="s">
         <v>9</v>
@@ -18898,16 +18883,16 @@
         <v>4</v>
       </c>
       <c r="B597" s="1" t="s">
-        <v>1187</v>
+        <v>1183</v>
       </c>
       <c r="C597" s="1" t="s">
-        <v>1188</v>
+        <v>1184</v>
       </c>
       <c r="D597" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E597" s="1" t="s">
-        <v>160</v>
+        <v>8</v>
       </c>
       <c r="F597" s="1" t="s">
         <v>9</v>
@@ -18921,16 +18906,16 @@
         <v>4</v>
       </c>
       <c r="B598" s="1" t="s">
-        <v>1189</v>
+        <v>1185</v>
       </c>
       <c r="C598" s="1" t="s">
-        <v>1190</v>
+        <v>1186</v>
       </c>
       <c r="D598" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E598" s="1" t="s">
-        <v>1191</v>
+        <v>160</v>
       </c>
       <c r="F598" s="1" t="s">
         <v>9</v>
@@ -18944,16 +18929,16 @@
         <v>4</v>
       </c>
       <c r="B599" s="1" t="s">
-        <v>1192</v>
+        <v>1187</v>
       </c>
       <c r="C599" s="1" t="s">
-        <v>1193</v>
+        <v>1188</v>
       </c>
       <c r="D599" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E599" s="1" t="s">
-        <v>94</v>
+        <v>1189</v>
       </c>
       <c r="F599" s="1" t="s">
         <v>9</v>
@@ -18967,16 +18952,16 @@
         <v>4</v>
       </c>
       <c r="B600" s="1" t="s">
-        <v>1194</v>
+        <v>1190</v>
       </c>
       <c r="C600" s="1" t="s">
-        <v>1195</v>
+        <v>1191</v>
       </c>
       <c r="D600" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E600" s="1" t="s">
-        <v>349</v>
+        <v>94</v>
       </c>
       <c r="F600" s="1" t="s">
         <v>9</v>
@@ -18990,16 +18975,16 @@
         <v>4</v>
       </c>
       <c r="B601" s="1" t="s">
-        <v>1196</v>
+        <v>1192</v>
       </c>
       <c r="C601" s="1" t="s">
-        <v>1197</v>
+        <v>1193</v>
       </c>
       <c r="D601" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E601" s="1" t="s">
-        <v>163</v>
+        <v>220</v>
       </c>
       <c r="F601" s="1" t="s">
         <v>9</v>
@@ -19013,16 +18998,16 @@
         <v>4</v>
       </c>
       <c r="B602" s="1" t="s">
-        <v>1198</v>
+        <v>1194</v>
       </c>
       <c r="C602" s="1" t="s">
-        <v>1199</v>
+        <v>1195</v>
       </c>
       <c r="D602" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E602" s="1" t="s">
-        <v>64</v>
+        <v>163</v>
       </c>
       <c r="F602" s="1" t="s">
         <v>9</v>
@@ -19036,16 +19021,16 @@
         <v>4</v>
       </c>
       <c r="B603" s="1" t="s">
-        <v>1200</v>
+        <v>1196</v>
       </c>
       <c r="C603" s="1" t="s">
-        <v>1201</v>
+        <v>1197</v>
       </c>
       <c r="D603" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E603" s="1" t="s">
-        <v>94</v>
+        <v>64</v>
       </c>
       <c r="F603" s="1" t="s">
         <v>9</v>
@@ -19059,16 +19044,16 @@
         <v>4</v>
       </c>
       <c r="B604" s="1" t="s">
-        <v>1202</v>
+        <v>1198</v>
       </c>
       <c r="C604" s="1" t="s">
-        <v>1203</v>
+        <v>1199</v>
       </c>
       <c r="D604" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E604" s="1" t="s">
-        <v>8</v>
+        <v>349</v>
       </c>
       <c r="F604" s="1" t="s">
         <v>9</v>
@@ -19082,16 +19067,16 @@
         <v>4</v>
       </c>
       <c r="B605" s="1" t="s">
-        <v>1202</v>
+        <v>1200</v>
       </c>
       <c r="C605" s="1" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
       <c r="D605" s="1" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E605" s="1" t="s">
-        <v>97</v>
+        <v>43</v>
       </c>
       <c r="F605" s="1" t="s">
         <v>9</v>
@@ -19105,16 +19090,16 @@
         <v>4</v>
       </c>
       <c r="B606" s="1" t="s">
-        <v>1204</v>
+        <v>1200</v>
       </c>
       <c r="C606" s="1" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D606" s="1" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E606" s="1" t="s">
-        <v>613</v>
+        <v>97</v>
       </c>
       <c r="F606" s="1" t="s">
         <v>9</v>
@@ -19128,16 +19113,16 @@
         <v>4</v>
       </c>
       <c r="B607" s="1" t="s">
-        <v>1206</v>
+        <v>1202</v>
       </c>
       <c r="C607" s="1" t="s">
-        <v>1207</v>
+        <v>1203</v>
       </c>
       <c r="D607" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E607" s="1" t="s">
-        <v>170</v>
+        <v>613</v>
       </c>
       <c r="F607" s="1" t="s">
         <v>9</v>
@@ -19151,16 +19136,16 @@
         <v>4</v>
       </c>
       <c r="B608" s="1" t="s">
-        <v>1407</v>
+        <v>1204</v>
       </c>
       <c r="C608" s="1" t="s">
-        <v>1408</v>
+        <v>1205</v>
       </c>
       <c r="D608" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E608" s="1" t="s">
-        <v>94</v>
+        <v>170</v>
       </c>
       <c r="F608" s="1" t="s">
         <v>9</v>
@@ -19174,16 +19159,16 @@
         <v>4</v>
       </c>
       <c r="B609" s="1" t="s">
-        <v>1208</v>
+        <v>1404</v>
       </c>
       <c r="C609" s="1" t="s">
-        <v>1209</v>
+        <v>1405</v>
       </c>
       <c r="D609" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E609" s="1" t="s">
-        <v>160</v>
+        <v>349</v>
       </c>
       <c r="F609" s="1" t="s">
         <v>9</v>
@@ -19197,16 +19182,16 @@
         <v>4</v>
       </c>
       <c r="B610" s="1" t="s">
-        <v>1210</v>
+        <v>1206</v>
       </c>
       <c r="C610" s="1" t="s">
-        <v>1211</v>
+        <v>1207</v>
       </c>
       <c r="D610" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E610" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F610" s="1" t="s">
         <v>9</v>
@@ -19220,16 +19205,16 @@
         <v>4</v>
       </c>
       <c r="B611" s="1" t="s">
-        <v>1212</v>
+        <v>1208</v>
       </c>
       <c r="C611" s="1" t="s">
-        <v>1213</v>
+        <v>1209</v>
       </c>
       <c r="D611" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E611" s="1" t="s">
-        <v>271</v>
+        <v>64</v>
       </c>
       <c r="F611" s="1" t="s">
         <v>9</v>
@@ -19243,16 +19228,16 @@
         <v>4</v>
       </c>
       <c r="B612" s="1" t="s">
-        <v>1214</v>
+        <v>1210</v>
       </c>
       <c r="C612" s="1" t="s">
-        <v>1215</v>
+        <v>1211</v>
       </c>
       <c r="D612" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E612" s="1" t="s">
-        <v>163</v>
+        <v>271</v>
       </c>
       <c r="F612" s="1" t="s">
         <v>9</v>
@@ -19266,16 +19251,16 @@
         <v>4</v>
       </c>
       <c r="B613" s="1" t="s">
-        <v>1216</v>
+        <v>1212</v>
       </c>
       <c r="C613" s="1" t="s">
-        <v>1217</v>
+        <v>1213</v>
       </c>
       <c r="D613" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E613" s="1" t="s">
-        <v>1191</v>
+        <v>163</v>
       </c>
       <c r="F613" s="1" t="s">
         <v>9</v>
@@ -19289,16 +19274,16 @@
         <v>4</v>
       </c>
       <c r="B614" s="1" t="s">
-        <v>1218</v>
+        <v>1214</v>
       </c>
       <c r="C614" s="1" t="s">
-        <v>1219</v>
+        <v>1215</v>
       </c>
       <c r="D614" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E614" s="1" t="s">
-        <v>55</v>
+        <v>1189</v>
       </c>
       <c r="F614" s="1" t="s">
         <v>9</v>
@@ -19312,16 +19297,16 @@
         <v>4</v>
       </c>
       <c r="B615" s="1" t="s">
-        <v>1220</v>
+        <v>1216</v>
       </c>
       <c r="C615" s="1" t="s">
-        <v>1221</v>
+        <v>1217</v>
       </c>
       <c r="D615" s="1" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E615" s="1" t="s">
-        <v>1391</v>
+        <v>55</v>
       </c>
       <c r="F615" s="1" t="s">
         <v>9</v>
@@ -19335,16 +19320,16 @@
         <v>4</v>
       </c>
       <c r="B616" s="1" t="s">
-        <v>1222</v>
+        <v>1218</v>
       </c>
       <c r="C616" s="1" t="s">
-        <v>1223</v>
+        <v>1219</v>
       </c>
       <c r="D616" s="1" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="E616" s="1" t="s">
-        <v>72</v>
+        <v>1389</v>
       </c>
       <c r="F616" s="1" t="s">
         <v>9</v>
@@ -19358,16 +19343,16 @@
         <v>4</v>
       </c>
       <c r="B617" s="1" t="s">
-        <v>1482</v>
+        <v>1220</v>
       </c>
       <c r="C617" s="1" t="s">
-        <v>1483</v>
+        <v>1221</v>
       </c>
       <c r="D617" s="1" t="s">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="E617" s="1" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="F617" s="1" t="s">
         <v>9</v>
@@ -19381,16 +19366,16 @@
         <v>4</v>
       </c>
       <c r="B618" s="1" t="s">
-        <v>1224</v>
+        <v>1474</v>
       </c>
       <c r="C618" s="1" t="s">
-        <v>1225</v>
+        <v>1475</v>
       </c>
       <c r="D618" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E618" s="1" t="s">
-        <v>170</v>
+        <v>52</v>
       </c>
       <c r="F618" s="1" t="s">
         <v>9</v>
@@ -19404,16 +19389,16 @@
         <v>4</v>
       </c>
       <c r="B619" s="1" t="s">
-        <v>1226</v>
+        <v>1222</v>
       </c>
       <c r="C619" s="1" t="s">
-        <v>1227</v>
+        <v>1223</v>
       </c>
       <c r="D619" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E619" s="1" t="s">
-        <v>18</v>
+        <v>170</v>
       </c>
       <c r="F619" s="1" t="s">
         <v>9</v>
@@ -19427,10 +19412,10 @@
         <v>4</v>
       </c>
       <c r="B620" s="1" t="s">
-        <v>1228</v>
+        <v>1224</v>
       </c>
       <c r="C620" s="1" t="s">
-        <v>1229</v>
+        <v>1225</v>
       </c>
       <c r="D620" s="1" t="s">
         <v>7</v>
@@ -19450,16 +19435,16 @@
         <v>4</v>
       </c>
       <c r="B621" s="1" t="s">
-        <v>1230</v>
+        <v>1226</v>
       </c>
       <c r="C621" s="1" t="s">
-        <v>1231</v>
+        <v>1227</v>
       </c>
       <c r="D621" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E621" s="1" t="s">
-        <v>410</v>
+        <v>30</v>
       </c>
       <c r="F621" s="1" t="s">
         <v>9</v>
@@ -19473,16 +19458,16 @@
         <v>4</v>
       </c>
       <c r="B622" s="1" t="s">
-        <v>1232</v>
+        <v>1228</v>
       </c>
       <c r="C622" s="1" t="s">
-        <v>1233</v>
+        <v>1229</v>
       </c>
       <c r="D622" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E622" s="1" t="s">
-        <v>8</v>
+        <v>410</v>
       </c>
       <c r="F622" s="1" t="s">
         <v>9</v>
@@ -19496,16 +19481,16 @@
         <v>4</v>
       </c>
       <c r="B623" s="1" t="s">
-        <v>1234</v>
+        <v>1230</v>
       </c>
       <c r="C623" s="1" t="s">
-        <v>1235</v>
+        <v>1231</v>
       </c>
       <c r="D623" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E623" s="1" t="s">
-        <v>558</v>
+        <v>8</v>
       </c>
       <c r="F623" s="1" t="s">
         <v>9</v>
@@ -19519,16 +19504,16 @@
         <v>4</v>
       </c>
       <c r="B624" s="1" t="s">
-        <v>1570</v>
+        <v>1232</v>
       </c>
       <c r="C624" s="1" t="s">
-        <v>1571</v>
+        <v>1233</v>
       </c>
       <c r="D624" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E624" s="1" t="s">
-        <v>52</v>
+        <v>558</v>
       </c>
       <c r="F624" s="1" t="s">
         <v>9</v>
@@ -19542,10 +19527,10 @@
         <v>4</v>
       </c>
       <c r="B625" s="1" t="s">
-        <v>1236</v>
+        <v>1512</v>
       </c>
       <c r="C625" s="1" t="s">
-        <v>1237</v>
+        <v>1513</v>
       </c>
       <c r="D625" s="1" t="s">
         <v>7</v>
@@ -19565,16 +19550,16 @@
         <v>4</v>
       </c>
       <c r="B626" s="1" t="s">
-        <v>1238</v>
+        <v>1234</v>
       </c>
       <c r="C626" s="1" t="s">
-        <v>1239</v>
+        <v>1235</v>
       </c>
       <c r="D626" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E626" s="1" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="F626" s="1" t="s">
         <v>9</v>
@@ -19588,16 +19573,16 @@
         <v>4</v>
       </c>
       <c r="B627" s="1" t="s">
-        <v>1240</v>
+        <v>1236</v>
       </c>
       <c r="C627" s="1" t="s">
-        <v>1241</v>
+        <v>1237</v>
       </c>
       <c r="D627" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E627" s="1" t="s">
-        <v>1522</v>
+        <v>67</v>
       </c>
       <c r="F627" s="1" t="s">
         <v>9</v>
@@ -19611,16 +19596,16 @@
         <v>4</v>
       </c>
       <c r="B628" s="1" t="s">
-        <v>1242</v>
+        <v>1238</v>
       </c>
       <c r="C628" s="1" t="s">
-        <v>1243</v>
+        <v>1239</v>
       </c>
       <c r="D628" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E628" s="1" t="s">
-        <v>1572</v>
+        <v>1575</v>
       </c>
       <c r="F628" s="1" t="s">
         <v>9</v>
@@ -19634,16 +19619,16 @@
         <v>4</v>
       </c>
       <c r="B629" s="1" t="s">
-        <v>1244</v>
+        <v>1240</v>
       </c>
       <c r="C629" s="1" t="s">
-        <v>1245</v>
+        <v>1241</v>
       </c>
       <c r="D629" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E629" s="1" t="s">
-        <v>94</v>
+        <v>812</v>
       </c>
       <c r="F629" s="1" t="s">
         <v>9</v>
@@ -19657,16 +19642,16 @@
         <v>4</v>
       </c>
       <c r="B630" s="1" t="s">
-        <v>1246</v>
+        <v>1242</v>
       </c>
       <c r="C630" s="1" t="s">
-        <v>1247</v>
+        <v>1243</v>
       </c>
       <c r="D630" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E630" s="1" t="s">
-        <v>18</v>
+        <v>94</v>
       </c>
       <c r="F630" s="1" t="s">
         <v>9</v>
@@ -19680,16 +19665,16 @@
         <v>4</v>
       </c>
       <c r="B631" s="1" t="s">
-        <v>1248</v>
+        <v>1244</v>
       </c>
       <c r="C631" s="1" t="s">
-        <v>1249</v>
+        <v>1245</v>
       </c>
       <c r="D631" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E631" s="1" t="s">
-        <v>1497</v>
+        <v>18</v>
       </c>
       <c r="F631" s="1" t="s">
         <v>9</v>
@@ -19703,16 +19688,16 @@
         <v>4</v>
       </c>
       <c r="B632" s="1" t="s">
-        <v>1250</v>
+        <v>1246</v>
       </c>
       <c r="C632" s="1" t="s">
-        <v>1251</v>
+        <v>1247</v>
       </c>
       <c r="D632" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E632" s="1" t="s">
-        <v>1252</v>
+        <v>1485</v>
       </c>
       <c r="F632" s="1" t="s">
         <v>9</v>
@@ -19726,16 +19711,16 @@
         <v>4</v>
       </c>
       <c r="B633" s="1" t="s">
-        <v>1253</v>
+        <v>1248</v>
       </c>
       <c r="C633" s="1" t="s">
-        <v>1254</v>
+        <v>1249</v>
       </c>
       <c r="D633" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E633" s="1" t="s">
-        <v>46</v>
+        <v>1250</v>
       </c>
       <c r="F633" s="1" t="s">
         <v>9</v>
@@ -19749,16 +19734,16 @@
         <v>4</v>
       </c>
       <c r="B634" s="1" t="s">
-        <v>1255</v>
+        <v>1251</v>
       </c>
       <c r="C634" s="1" t="s">
-        <v>1256</v>
+        <v>1252</v>
       </c>
       <c r="D634" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E634" s="1" t="s">
-        <v>477</v>
+        <v>46</v>
       </c>
       <c r="F634" s="1" t="s">
         <v>9</v>
@@ -19772,16 +19757,16 @@
         <v>4</v>
       </c>
       <c r="B635" s="1" t="s">
-        <v>1257</v>
+        <v>1253</v>
       </c>
       <c r="C635" s="1" t="s">
-        <v>1258</v>
+        <v>1254</v>
       </c>
       <c r="D635" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E635" s="1" t="s">
-        <v>451</v>
+        <v>1467</v>
       </c>
       <c r="F635" s="1" t="s">
         <v>9</v>
@@ -19795,16 +19780,16 @@
         <v>4</v>
       </c>
       <c r="B636" s="1" t="s">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="C636" s="1" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
       <c r="D636" s="1" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E636" s="1" t="s">
-        <v>653</v>
+        <v>451</v>
       </c>
       <c r="F636" s="1" t="s">
         <v>9</v>
@@ -19818,19 +19803,19 @@
         <v>4</v>
       </c>
       <c r="B637" s="1" t="s">
-        <v>1259</v>
+        <v>1255</v>
       </c>
       <c r="C637" s="1" t="s">
-        <v>1260</v>
+        <v>1256</v>
       </c>
       <c r="D637" s="1" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E637" s="1" t="s">
-        <v>466</v>
+        <v>653</v>
       </c>
       <c r="F637" s="1" t="s">
-        <v>112</v>
+        <v>9</v>
       </c>
       <c r="G637" s="1" t="s">
         <v>10</v>
@@ -19841,16 +19826,16 @@
         <v>4</v>
       </c>
       <c r="B638" s="1" t="s">
-        <v>1261</v>
+        <v>1257</v>
       </c>
       <c r="C638" s="1" t="s">
-        <v>1262</v>
+        <v>1258</v>
       </c>
       <c r="D638" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E638" s="1" t="s">
-        <v>116</v>
+        <v>466</v>
       </c>
       <c r="F638" s="1" t="s">
         <v>112</v>
@@ -19864,19 +19849,19 @@
         <v>4</v>
       </c>
       <c r="B639" s="1" t="s">
-        <v>1263</v>
+        <v>1259</v>
       </c>
       <c r="C639" s="1" t="s">
-        <v>1264</v>
+        <v>1260</v>
       </c>
       <c r="D639" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E639" s="1" t="s">
-        <v>30</v>
+        <v>116</v>
       </c>
       <c r="F639" s="1" t="s">
-        <v>9</v>
+        <v>112</v>
       </c>
       <c r="G639" s="1" t="s">
         <v>10</v>
@@ -19887,16 +19872,16 @@
         <v>4</v>
       </c>
       <c r="B640" s="1" t="s">
-        <v>1265</v>
+        <v>1261</v>
       </c>
       <c r="C640" s="1" t="s">
-        <v>1266</v>
+        <v>1262</v>
       </c>
       <c r="D640" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E640" s="1" t="s">
-        <v>466</v>
+        <v>30</v>
       </c>
       <c r="F640" s="1" t="s">
         <v>9</v>
@@ -19910,16 +19895,16 @@
         <v>4</v>
       </c>
       <c r="B641" s="1" t="s">
-        <v>1267</v>
+        <v>1263</v>
       </c>
       <c r="C641" s="1" t="s">
-        <v>1268</v>
+        <v>1264</v>
       </c>
       <c r="D641" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E641" s="1" t="s">
-        <v>163</v>
+        <v>466</v>
       </c>
       <c r="F641" s="1" t="s">
         <v>9</v>
@@ -19933,16 +19918,16 @@
         <v>4</v>
       </c>
       <c r="B642" s="1" t="s">
-        <v>1269</v>
+        <v>1265</v>
       </c>
       <c r="C642" s="1" t="s">
-        <v>1270</v>
+        <v>1266</v>
       </c>
       <c r="D642" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E642" s="1" t="s">
-        <v>1573</v>
+        <v>163</v>
       </c>
       <c r="F642" s="1" t="s">
         <v>9</v>
@@ -19956,16 +19941,16 @@
         <v>4</v>
       </c>
       <c r="B643" s="1" t="s">
-        <v>1271</v>
+        <v>1267</v>
       </c>
       <c r="C643" s="1" t="s">
-        <v>1272</v>
+        <v>1268</v>
       </c>
       <c r="D643" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E643" s="1" t="s">
-        <v>58</v>
+        <v>1515</v>
       </c>
       <c r="F643" s="1" t="s">
         <v>9</v>
@@ -19979,16 +19964,16 @@
         <v>4</v>
       </c>
       <c r="B644" s="1" t="s">
-        <v>1273</v>
+        <v>1269</v>
       </c>
       <c r="C644" s="1" t="s">
-        <v>1274</v>
+        <v>1270</v>
       </c>
       <c r="D644" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E644" s="1" t="s">
-        <v>466</v>
+        <v>58</v>
       </c>
       <c r="F644" s="1" t="s">
         <v>9</v>
@@ -20002,16 +19987,16 @@
         <v>4</v>
       </c>
       <c r="B645" s="1" t="s">
-        <v>1275</v>
+        <v>1271</v>
       </c>
       <c r="C645" s="1" t="s">
-        <v>1276</v>
+        <v>1272</v>
       </c>
       <c r="D645" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E645" s="1" t="s">
-        <v>306</v>
+        <v>466</v>
       </c>
       <c r="F645" s="1" t="s">
         <v>9</v>
@@ -20025,16 +20010,16 @@
         <v>4</v>
       </c>
       <c r="B646" s="1" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="C646" s="1" t="s">
-        <v>1278</v>
+        <v>1274</v>
       </c>
       <c r="D646" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E646" s="1" t="s">
-        <v>157</v>
+        <v>306</v>
       </c>
       <c r="F646" s="1" t="s">
         <v>9</v>
@@ -20048,16 +20033,16 @@
         <v>4</v>
       </c>
       <c r="B647" s="1" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="C647" s="1" t="s">
-        <v>1280</v>
+        <v>1276</v>
       </c>
       <c r="D647" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E647" s="1" t="s">
-        <v>1281</v>
+        <v>157</v>
       </c>
       <c r="F647" s="1" t="s">
         <v>9</v>
@@ -20071,16 +20056,16 @@
         <v>4</v>
       </c>
       <c r="B648" s="1" t="s">
-        <v>1282</v>
+        <v>1277</v>
       </c>
       <c r="C648" s="1" t="s">
-        <v>1283</v>
+        <v>1278</v>
       </c>
       <c r="D648" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E648" s="1" t="s">
-        <v>466</v>
+        <v>1279</v>
       </c>
       <c r="F648" s="1" t="s">
         <v>9</v>
@@ -20094,16 +20079,16 @@
         <v>4</v>
       </c>
       <c r="B649" s="1" t="s">
-        <v>1284</v>
+        <v>1280</v>
       </c>
       <c r="C649" s="1" t="s">
-        <v>1285</v>
+        <v>1281</v>
       </c>
       <c r="D649" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E649" s="1" t="s">
-        <v>1286</v>
+        <v>466</v>
       </c>
       <c r="F649" s="1" t="s">
         <v>9</v>
@@ -20117,16 +20102,16 @@
         <v>4</v>
       </c>
       <c r="B650" s="1" t="s">
-        <v>1287</v>
+        <v>1282</v>
       </c>
       <c r="C650" s="1" t="s">
-        <v>1288</v>
+        <v>1283</v>
       </c>
       <c r="D650" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E650" s="1" t="s">
-        <v>18</v>
+        <v>1284</v>
       </c>
       <c r="F650" s="1" t="s">
         <v>9</v>
@@ -20140,16 +20125,16 @@
         <v>4</v>
       </c>
       <c r="B651" s="1" t="s">
-        <v>1289</v>
+        <v>1285</v>
       </c>
       <c r="C651" s="1" t="s">
-        <v>1290</v>
+        <v>1286</v>
       </c>
       <c r="D651" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E651" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F651" s="1" t="s">
         <v>9</v>
@@ -20163,16 +20148,16 @@
         <v>4</v>
       </c>
       <c r="B652" s="1" t="s">
-        <v>1291</v>
+        <v>1287</v>
       </c>
       <c r="C652" s="1" t="s">
-        <v>1292</v>
+        <v>1288</v>
       </c>
       <c r="D652" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E652" s="1" t="s">
-        <v>1293</v>
+        <v>160</v>
       </c>
       <c r="F652" s="1" t="s">
         <v>9</v>
@@ -20186,16 +20171,16 @@
         <v>4</v>
       </c>
       <c r="B653" s="1" t="s">
-        <v>1294</v>
+        <v>1289</v>
       </c>
       <c r="C653" s="1" t="s">
-        <v>1295</v>
+        <v>1290</v>
       </c>
       <c r="D653" s="1" t="s">
-        <v>1296</v>
+        <v>7</v>
       </c>
       <c r="E653" s="1" t="s">
-        <v>98</v>
+        <v>1291</v>
       </c>
       <c r="F653" s="1" t="s">
         <v>9</v>
@@ -20209,16 +20194,16 @@
         <v>4</v>
       </c>
       <c r="B654" s="1" t="s">
-        <v>1297</v>
+        <v>1292</v>
       </c>
       <c r="C654" s="1" t="s">
-        <v>1298</v>
+        <v>1293</v>
       </c>
       <c r="D654" s="1" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="E654" s="1" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="F654" s="1" t="s">
         <v>9</v>
@@ -20232,16 +20217,16 @@
         <v>4</v>
       </c>
       <c r="B655" s="1" t="s">
-        <v>1299</v>
+        <v>1295</v>
       </c>
       <c r="C655" s="1" t="s">
-        <v>1300</v>
+        <v>1296</v>
       </c>
       <c r="D655" s="1" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="E655" s="1" t="s">
-        <v>1424</v>
+        <v>94</v>
       </c>
       <c r="F655" s="1" t="s">
         <v>9</v>
@@ -20255,16 +20240,16 @@
         <v>4</v>
       </c>
       <c r="B656" s="1" t="s">
-        <v>1301</v>
+        <v>1297</v>
       </c>
       <c r="C656" s="1" t="s">
-        <v>1302</v>
+        <v>1298</v>
       </c>
       <c r="D656" s="1" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="E656" s="1" t="s">
-        <v>46</v>
+        <v>1420</v>
       </c>
       <c r="F656" s="1" t="s">
         <v>9</v>
@@ -20278,16 +20263,16 @@
         <v>4</v>
       </c>
       <c r="B657" s="1" t="s">
-        <v>1303</v>
+        <v>1299</v>
       </c>
       <c r="C657" s="1" t="s">
-        <v>1304</v>
+        <v>1300</v>
       </c>
       <c r="D657" s="1" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="E657" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F657" s="1" t="s">
         <v>9</v>
@@ -20301,16 +20286,16 @@
         <v>4</v>
       </c>
       <c r="B658" s="1" t="s">
-        <v>1305</v>
+        <v>1301</v>
       </c>
       <c r="C658" s="1" t="s">
-        <v>1306</v>
+        <v>1302</v>
       </c>
       <c r="D658" s="1" t="s">
-        <v>7</v>
+        <v>1294</v>
       </c>
       <c r="E658" s="1" t="s">
-        <v>563</v>
+        <v>43</v>
       </c>
       <c r="F658" s="1" t="s">
         <v>9</v>
@@ -20324,19 +20309,19 @@
         <v>4</v>
       </c>
       <c r="B659" s="1" t="s">
-        <v>1467</v>
+        <v>1303</v>
       </c>
       <c r="C659" s="1" t="s">
-        <v>1468</v>
+        <v>1304</v>
       </c>
       <c r="D659" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E659" s="1" t="s">
-        <v>242</v>
+        <v>563</v>
       </c>
       <c r="F659" s="1" t="s">
-        <v>112</v>
+        <v>9</v>
       </c>
       <c r="G659" s="1" t="s">
         <v>10</v>
@@ -20347,19 +20332,19 @@
         <v>4</v>
       </c>
       <c r="B660" s="1" t="s">
-        <v>1307</v>
+        <v>1462</v>
       </c>
       <c r="C660" s="1" t="s">
-        <v>1308</v>
+        <v>1463</v>
       </c>
       <c r="D660" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E660" s="1" t="s">
-        <v>52</v>
+        <v>242</v>
       </c>
       <c r="F660" s="1" t="s">
-        <v>9</v>
+        <v>112</v>
       </c>
       <c r="G660" s="1" t="s">
         <v>10</v>
@@ -20370,16 +20355,16 @@
         <v>4</v>
       </c>
       <c r="B661" s="1" t="s">
-        <v>1309</v>
+        <v>1305</v>
       </c>
       <c r="C661" s="1" t="s">
-        <v>1310</v>
+        <v>1306</v>
       </c>
       <c r="D661" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E661" s="1" t="s">
-        <v>148</v>
+        <v>52</v>
       </c>
       <c r="F661" s="1" t="s">
         <v>9</v>
@@ -20393,16 +20378,16 @@
         <v>4</v>
       </c>
       <c r="B662" s="1" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="C662" s="1" t="s">
-        <v>1310</v>
+        <v>1308</v>
       </c>
       <c r="D662" s="1" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E662" s="1" t="s">
-        <v>492</v>
+        <v>148</v>
       </c>
       <c r="F662" s="1" t="s">
         <v>9</v>
@@ -20416,16 +20401,16 @@
         <v>4</v>
       </c>
       <c r="B663" s="1" t="s">
-        <v>1311</v>
+        <v>1307</v>
       </c>
       <c r="C663" s="1" t="s">
-        <v>1312</v>
+        <v>1308</v>
       </c>
       <c r="D663" s="1" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E663" s="1" t="s">
-        <v>593</v>
+        <v>492</v>
       </c>
       <c r="F663" s="1" t="s">
         <v>9</v>
@@ -20439,16 +20424,16 @@
         <v>4</v>
       </c>
       <c r="B664" s="1" t="s">
-        <v>1313</v>
+        <v>1309</v>
       </c>
       <c r="C664" s="1" t="s">
-        <v>1314</v>
+        <v>1310</v>
       </c>
       <c r="D664" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E664" s="1" t="s">
-        <v>1519</v>
+        <v>1576</v>
       </c>
       <c r="F664" s="1" t="s">
         <v>9</v>
@@ -20462,16 +20447,16 @@
         <v>4</v>
       </c>
       <c r="B665" s="1" t="s">
-        <v>1315</v>
+        <v>1311</v>
       </c>
       <c r="C665" s="1" t="s">
-        <v>1316</v>
+        <v>1312</v>
       </c>
       <c r="D665" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E665" s="1" t="s">
-        <v>270</v>
+        <v>1577</v>
       </c>
       <c r="F665" s="1" t="s">
         <v>9</v>
@@ -20485,16 +20470,16 @@
         <v>4</v>
       </c>
       <c r="B666" s="1" t="s">
-        <v>1317</v>
+        <v>1313</v>
       </c>
       <c r="C666" s="1" t="s">
-        <v>1318</v>
+        <v>1314</v>
       </c>
       <c r="D666" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E666" s="1" t="s">
-        <v>1574</v>
+        <v>270</v>
       </c>
       <c r="F666" s="1" t="s">
         <v>9</v>
@@ -20508,19 +20493,19 @@
         <v>4</v>
       </c>
       <c r="B667" s="1" t="s">
-        <v>1319</v>
+        <v>1315</v>
       </c>
       <c r="C667" s="1" t="s">
-        <v>1320</v>
+        <v>1316</v>
       </c>
       <c r="D667" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E667" s="1" t="s">
-        <v>492</v>
+        <v>1578</v>
       </c>
       <c r="F667" s="1" t="s">
-        <v>112</v>
+        <v>9</v>
       </c>
       <c r="G667" s="1" t="s">
         <v>10</v>
@@ -20531,19 +20516,19 @@
         <v>4</v>
       </c>
       <c r="B668" s="1" t="s">
-        <v>1321</v>
+        <v>1317</v>
       </c>
       <c r="C668" s="1" t="s">
-        <v>1322</v>
+        <v>1318</v>
       </c>
       <c r="D668" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E668" s="1" t="s">
-        <v>97</v>
+        <v>492</v>
       </c>
       <c r="F668" s="1" t="s">
-        <v>9</v>
+        <v>112</v>
       </c>
       <c r="G668" s="1" t="s">
         <v>10</v>
@@ -20554,16 +20539,16 @@
         <v>4</v>
       </c>
       <c r="B669" s="1" t="s">
-        <v>1323</v>
+        <v>1319</v>
       </c>
       <c r="C669" s="1" t="s">
-        <v>1324</v>
+        <v>1320</v>
       </c>
       <c r="D669" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E669" s="1" t="s">
-        <v>1575</v>
+        <v>141</v>
       </c>
       <c r="F669" s="1" t="s">
         <v>9</v>
@@ -20577,16 +20562,16 @@
         <v>4</v>
       </c>
       <c r="B670" s="1" t="s">
-        <v>1325</v>
+        <v>1321</v>
       </c>
       <c r="C670" s="1" t="s">
-        <v>1326</v>
+        <v>1322</v>
       </c>
       <c r="D670" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E670" s="1" t="s">
-        <v>1327</v>
+        <v>1579</v>
       </c>
       <c r="F670" s="1" t="s">
         <v>9</v>
@@ -20600,16 +20585,16 @@
         <v>4</v>
       </c>
       <c r="B671" s="1" t="s">
-        <v>1328</v>
+        <v>1323</v>
       </c>
       <c r="C671" s="1" t="s">
-        <v>1329</v>
+        <v>1324</v>
       </c>
       <c r="D671" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E671" s="1" t="s">
-        <v>64</v>
+        <v>1325</v>
       </c>
       <c r="F671" s="1" t="s">
         <v>9</v>
@@ -20623,16 +20608,16 @@
         <v>4</v>
       </c>
       <c r="B672" s="1" t="s">
-        <v>1409</v>
+        <v>1326</v>
       </c>
       <c r="C672" s="1" t="s">
-        <v>1410</v>
+        <v>1327</v>
       </c>
       <c r="D672" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E672" s="1" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="F672" s="1" t="s">
         <v>9</v>
@@ -20646,16 +20631,16 @@
         <v>4</v>
       </c>
       <c r="B673" s="1" t="s">
-        <v>1330</v>
+        <v>1406</v>
       </c>
       <c r="C673" s="1" t="s">
-        <v>1331</v>
+        <v>1407</v>
       </c>
       <c r="D673" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E673" s="1" t="s">
-        <v>263</v>
+        <v>46</v>
       </c>
       <c r="F673" s="1" t="s">
         <v>9</v>
@@ -20669,16 +20654,16 @@
         <v>4</v>
       </c>
       <c r="B674" s="1" t="s">
-        <v>1332</v>
+        <v>1328</v>
       </c>
       <c r="C674" s="1" t="s">
-        <v>1333</v>
+        <v>1329</v>
       </c>
       <c r="D674" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E674" s="1" t="s">
-        <v>922</v>
+        <v>563</v>
       </c>
       <c r="F674" s="1" t="s">
         <v>9</v>
@@ -20692,19 +20677,19 @@
         <v>4</v>
       </c>
       <c r="B675" s="1" t="s">
-        <v>1334</v>
+        <v>1330</v>
       </c>
       <c r="C675" s="1" t="s">
-        <v>1335</v>
+        <v>1331</v>
       </c>
       <c r="D675" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E675" s="1" t="s">
-        <v>1336</v>
+        <v>623</v>
       </c>
       <c r="F675" s="1" t="s">
-        <v>295</v>
+        <v>9</v>
       </c>
       <c r="G675" s="1" t="s">
         <v>10</v>
@@ -20715,16 +20700,16 @@
         <v>4</v>
       </c>
       <c r="B676" s="1" t="s">
-        <v>1337</v>
+        <v>1332</v>
       </c>
       <c r="C676" s="1" t="s">
-        <v>1338</v>
+        <v>1333</v>
       </c>
       <c r="D676" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E676" s="1" t="s">
-        <v>1339</v>
+        <v>1334</v>
       </c>
       <c r="F676" s="1" t="s">
         <v>295</v>
@@ -20738,19 +20723,19 @@
         <v>4</v>
       </c>
       <c r="B677" s="1" t="s">
-        <v>1340</v>
+        <v>1335</v>
       </c>
       <c r="C677" s="1" t="s">
-        <v>1341</v>
+        <v>1336</v>
       </c>
       <c r="D677" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E677" s="1" t="s">
-        <v>72</v>
+        <v>1337</v>
       </c>
       <c r="F677" s="1" t="s">
-        <v>112</v>
+        <v>295</v>
       </c>
       <c r="G677" s="1" t="s">
         <v>10</v>
@@ -20761,19 +20746,19 @@
         <v>4</v>
       </c>
       <c r="B678" s="1" t="s">
-        <v>1576</v>
+        <v>1338</v>
       </c>
       <c r="C678" s="1" t="s">
-        <v>1577</v>
+        <v>1339</v>
       </c>
       <c r="D678" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E678" s="1" t="s">
-        <v>27</v>
+        <v>72</v>
       </c>
       <c r="F678" s="1" t="s">
-        <v>9</v>
+        <v>112</v>
       </c>
       <c r="G678" s="1" t="s">
         <v>10</v>
@@ -20784,19 +20769,19 @@
         <v>4</v>
       </c>
       <c r="B679" s="1" t="s">
-        <v>1342</v>
+        <v>1516</v>
       </c>
       <c r="C679" s="1" t="s">
-        <v>1343</v>
+        <v>1517</v>
       </c>
       <c r="D679" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E679" s="1" t="s">
-        <v>466</v>
+        <v>27</v>
       </c>
       <c r="F679" s="1" t="s">
-        <v>112</v>
+        <v>9</v>
       </c>
       <c r="G679" s="1" t="s">
         <v>10</v>
@@ -20807,19 +20792,19 @@
         <v>4</v>
       </c>
       <c r="B680" s="1" t="s">
-        <v>1345</v>
+        <v>1340</v>
       </c>
       <c r="C680" s="1" t="s">
-        <v>1346</v>
+        <v>1341</v>
       </c>
       <c r="D680" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E680" s="1" t="s">
-        <v>922</v>
+        <v>466</v>
       </c>
       <c r="F680" s="1" t="s">
-        <v>9</v>
+        <v>112</v>
       </c>
       <c r="G680" s="1" t="s">
         <v>10</v>
@@ -20830,16 +20815,16 @@
         <v>4</v>
       </c>
       <c r="B681" s="1" t="s">
-        <v>1347</v>
+        <v>1343</v>
       </c>
       <c r="C681" s="1" t="s">
-        <v>1348</v>
+        <v>1344</v>
       </c>
       <c r="D681" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E681" s="1" t="s">
-        <v>1520</v>
+        <v>921</v>
       </c>
       <c r="F681" s="1" t="s">
         <v>9</v>
@@ -20853,16 +20838,16 @@
         <v>4</v>
       </c>
       <c r="B682" s="1" t="s">
-        <v>1349</v>
+        <v>1345</v>
       </c>
       <c r="C682" s="1" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
       <c r="D682" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E682" s="1" t="s">
-        <v>163</v>
+        <v>387</v>
       </c>
       <c r="F682" s="1" t="s">
         <v>9</v>
@@ -20876,16 +20861,16 @@
         <v>4</v>
       </c>
       <c r="B683" s="1" t="s">
-        <v>1351</v>
+        <v>1347</v>
       </c>
       <c r="C683" s="1" t="s">
-        <v>1352</v>
+        <v>1348</v>
       </c>
       <c r="D683" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E683" s="1" t="s">
-        <v>121</v>
+        <v>163</v>
       </c>
       <c r="F683" s="1" t="s">
         <v>9</v>
@@ -20899,16 +20884,16 @@
         <v>4</v>
       </c>
       <c r="B684" s="1" t="s">
-        <v>1351</v>
+        <v>1349</v>
       </c>
       <c r="C684" s="1" t="s">
-        <v>1352</v>
+        <v>1350</v>
       </c>
       <c r="D684" s="1" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E684" s="1" t="s">
-        <v>1353</v>
+        <v>37</v>
       </c>
       <c r="F684" s="1" t="s">
         <v>9</v>
@@ -20922,16 +20907,16 @@
         <v>4</v>
       </c>
       <c r="B685" s="1" t="s">
-        <v>1354</v>
+        <v>1349</v>
       </c>
       <c r="C685" s="1" t="s">
-        <v>1355</v>
+        <v>1350</v>
       </c>
       <c r="D685" s="1" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E685" s="1" t="s">
-        <v>82</v>
+        <v>1351</v>
       </c>
       <c r="F685" s="1" t="s">
         <v>9</v>
@@ -20945,16 +20930,16 @@
         <v>4</v>
       </c>
       <c r="B686" s="1" t="s">
-        <v>1356</v>
+        <v>1352</v>
       </c>
       <c r="C686" s="1" t="s">
-        <v>1357</v>
+        <v>1353</v>
       </c>
       <c r="D686" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E686" s="1" t="s">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="F686" s="1" t="s">
         <v>9</v>
@@ -20968,16 +20953,16 @@
         <v>4</v>
       </c>
       <c r="B687" s="1" t="s">
-        <v>1358</v>
+        <v>1354</v>
       </c>
       <c r="C687" s="1" t="s">
-        <v>1359</v>
+        <v>1355</v>
       </c>
       <c r="D687" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E687" s="1" t="s">
-        <v>671</v>
+        <v>160</v>
       </c>
       <c r="F687" s="1" t="s">
         <v>9</v>
@@ -20991,10 +20976,10 @@
         <v>4</v>
       </c>
       <c r="B688" s="1" t="s">
-        <v>1360</v>
+        <v>1356</v>
       </c>
       <c r="C688" s="1" t="s">
-        <v>1361</v>
+        <v>1357</v>
       </c>
       <c r="D688" s="1" t="s">
         <v>7</v>
@@ -21014,16 +20999,16 @@
         <v>4</v>
       </c>
       <c r="B689" s="1" t="s">
-        <v>1578</v>
+        <v>1358</v>
       </c>
       <c r="C689" s="1" t="s">
-        <v>1579</v>
+        <v>1359</v>
       </c>
       <c r="D689" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E689" s="1" t="s">
-        <v>466</v>
+        <v>1393</v>
       </c>
       <c r="F689" s="1" t="s">
         <v>9</v>
@@ -21037,16 +21022,16 @@
         <v>4</v>
       </c>
       <c r="B690" s="1" t="s">
-        <v>1362</v>
+        <v>1518</v>
       </c>
       <c r="C690" s="1" t="s">
-        <v>1363</v>
+        <v>1519</v>
       </c>
       <c r="D690" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E690" s="1" t="s">
-        <v>43</v>
+        <v>466</v>
       </c>
       <c r="F690" s="1" t="s">
         <v>9</v>
@@ -21060,16 +21045,16 @@
         <v>4</v>
       </c>
       <c r="B691" s="1" t="s">
-        <v>1364</v>
+        <v>1360</v>
       </c>
       <c r="C691" s="1" t="s">
-        <v>1365</v>
+        <v>1361</v>
       </c>
       <c r="D691" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E691" s="1" t="s">
-        <v>671</v>
+        <v>43</v>
       </c>
       <c r="F691" s="1" t="s">
         <v>9</v>
@@ -21083,16 +21068,16 @@
         <v>4</v>
       </c>
       <c r="B692" s="1" t="s">
-        <v>1366</v>
+        <v>1362</v>
       </c>
       <c r="C692" s="1" t="s">
-        <v>1367</v>
+        <v>1363</v>
       </c>
       <c r="D692" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E692" s="1" t="s">
-        <v>211</v>
+        <v>671</v>
       </c>
       <c r="F692" s="1" t="s">
         <v>9</v>
@@ -21106,16 +21091,16 @@
         <v>4</v>
       </c>
       <c r="B693" s="1" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="C693" s="1" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="D693" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E693" s="1" t="s">
-        <v>242</v>
+        <v>211</v>
       </c>
       <c r="F693" s="1" t="s">
         <v>9</v>
@@ -21129,16 +21114,16 @@
         <v>4</v>
       </c>
       <c r="B694" s="1" t="s">
-        <v>1368</v>
+        <v>1366</v>
       </c>
       <c r="C694" s="1" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
       <c r="D694" s="1" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E694" s="1" t="s">
-        <v>34</v>
+        <v>242</v>
       </c>
       <c r="F694" s="1" t="s">
         <v>9</v>
@@ -21152,16 +21137,16 @@
         <v>4</v>
       </c>
       <c r="B695" s="1" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="C695" s="1" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="D695" s="1" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E695" s="1" t="s">
-        <v>1580</v>
+        <v>34</v>
       </c>
       <c r="F695" s="1" t="s">
         <v>9</v>
@@ -21175,16 +21160,16 @@
         <v>4</v>
       </c>
       <c r="B696" s="1" t="s">
-        <v>1370</v>
+        <v>1368</v>
       </c>
       <c r="C696" s="1" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
       <c r="D696" s="1" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E696" s="1" t="s">
-        <v>466</v>
+        <v>779</v>
       </c>
       <c r="F696" s="1" t="s">
         <v>9</v>
@@ -21198,16 +21183,16 @@
         <v>4</v>
       </c>
       <c r="B697" s="1" t="s">
-        <v>1372</v>
+        <v>1368</v>
       </c>
       <c r="C697" s="1" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="D697" s="1" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E697" s="1" t="s">
-        <v>82</v>
+        <v>466</v>
       </c>
       <c r="F697" s="1" t="s">
         <v>9</v>
@@ -21221,16 +21206,16 @@
         <v>4</v>
       </c>
       <c r="B698" s="1" t="s">
-        <v>1458</v>
+        <v>1370</v>
       </c>
       <c r="C698" s="1" t="s">
-        <v>1459</v>
+        <v>1371</v>
       </c>
       <c r="D698" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E698" s="1" t="s">
-        <v>613</v>
+        <v>18</v>
       </c>
       <c r="F698" s="1" t="s">
         <v>9</v>
@@ -21244,16 +21229,16 @@
         <v>4</v>
       </c>
       <c r="B699" s="1" t="s">
-        <v>1374</v>
+        <v>1453</v>
       </c>
       <c r="C699" s="1" t="s">
-        <v>1375</v>
+        <v>1454</v>
       </c>
       <c r="D699" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E699" s="1" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="F699" s="1" t="s">
         <v>9</v>
@@ -21267,16 +21252,16 @@
         <v>4</v>
       </c>
       <c r="B700" s="1" t="s">
-        <v>1376</v>
+        <v>1372</v>
       </c>
       <c r="C700" s="1" t="s">
-        <v>1377</v>
+        <v>1373</v>
       </c>
       <c r="D700" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E700" s="1" t="s">
-        <v>349</v>
+        <v>622</v>
       </c>
       <c r="F700" s="1" t="s">
         <v>9</v>
@@ -21287,25 +21272,25 @@
     </row>
     <row r="701" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A701" s="1" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B701" s="1" t="s">
-        <v>0</v>
+        <v>1374</v>
       </c>
       <c r="C701" s="1" t="s">
-        <v>0</v>
+        <v>1375</v>
       </c>
       <c r="D701" s="1" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E701" s="1" t="s">
-        <v>0</v>
+        <v>349</v>
       </c>
       <c r="F701" s="1" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G701" s="1" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="702" spans="1:7" x14ac:dyDescent="0.2">
@@ -21322,13 +21307,13 @@
         <v>0</v>
       </c>
       <c r="E702" s="1" t="s">
-        <v>686</v>
+        <v>0</v>
       </c>
       <c r="F702" s="1" t="s">
-        <v>570</v>
+        <v>0</v>
       </c>
       <c r="G702" s="1" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="703" spans="1:7" x14ac:dyDescent="0.2">
@@ -21345,10 +21330,10 @@
         <v>0</v>
       </c>
       <c r="E703" s="1" t="s">
-        <v>1581</v>
+        <v>686</v>
       </c>
       <c r="F703" s="1" t="s">
-        <v>463</v>
+        <v>570</v>
       </c>
       <c r="G703" s="1" t="s">
         <v>10</v>
@@ -21368,10 +21353,10 @@
         <v>0</v>
       </c>
       <c r="E704" s="1" t="s">
-        <v>1582</v>
+        <v>1580</v>
       </c>
       <c r="F704" s="1" t="s">
-        <v>295</v>
+        <v>463</v>
       </c>
       <c r="G704" s="1" t="s">
         <v>10</v>
@@ -21391,13 +21376,13 @@
         <v>0</v>
       </c>
       <c r="E705" s="1" t="s">
-        <v>1583</v>
+        <v>1581</v>
       </c>
       <c r="F705" s="1" t="s">
-        <v>186</v>
+        <v>295</v>
       </c>
       <c r="G705" s="1" t="s">
-        <v>1411</v>
+        <v>10</v>
       </c>
     </row>
     <row r="706" spans="1:7" x14ac:dyDescent="0.2">
@@ -21414,13 +21399,13 @@
         <v>0</v>
       </c>
       <c r="E706" s="1" t="s">
-        <v>1584</v>
+        <v>1582</v>
       </c>
       <c r="F706" s="1" t="s">
-        <v>112</v>
+        <v>186</v>
       </c>
       <c r="G706" s="1" t="s">
-        <v>10</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="707" spans="1:7" x14ac:dyDescent="0.2">
@@ -21437,13 +21422,13 @@
         <v>0</v>
       </c>
       <c r="E707" s="1" t="s">
-        <v>1585</v>
+        <v>1583</v>
       </c>
       <c r="F707" s="1" t="s">
-        <v>9</v>
+        <v>112</v>
       </c>
       <c r="G707" s="1" t="s">
-        <v>1586</v>
+        <v>10</v>
       </c>
     </row>
     <row r="708" spans="1:7" x14ac:dyDescent="0.2">
@@ -21460,13 +21445,13 @@
         <v>0</v>
       </c>
       <c r="E708" s="1" t="s">
-        <v>1484</v>
+        <v>1584</v>
       </c>
       <c r="F708" s="1" t="s">
         <v>9</v>
       </c>
       <c r="G708" s="1" t="s">
-        <v>10</v>
+        <v>1521</v>
       </c>
     </row>
   </sheetData>
